--- a/metrics.xlsx
+++ b/metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Adata\FIT CVUT\5-2\DIP\monkey_challenge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07DAD36-1329-4F44-B05D-E332DDB479EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2911AA-CD04-4C93-838D-B2B688E9C95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4AB71DB6-ACBD-44C9-9C84-03BC41085FCB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{4AB71DB6-ACBD-44C9-9C84-03BC41085FCB}"/>
   </bookViews>
   <sheets>
     <sheet name="Lymphocytes" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="40">
   <si>
     <t>model</t>
   </si>
@@ -653,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5AC0FCE-89EB-4E8A-9A1B-0F9DA6253ADF}">
-  <dimension ref="B2:T40"/>
+  <dimension ref="B2:T46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4.28515625" customWidth="1"/>
@@ -779,7 +779,7 @@
         <v>0.58499999999999996</v>
       </c>
       <c r="L4" s="4">
-        <f>MAX(I4:K4)</f>
+        <f t="shared" ref="L4:L46" si="0">MAX(I4:K4)</f>
         <v>0.73299999999999998</v>
       </c>
       <c r="M4" s="2">
@@ -792,7 +792,7 @@
         <v>0.59299999999999997</v>
       </c>
       <c r="P4" s="4">
-        <f>MAX(M4:O4)</f>
+        <f t="shared" ref="P4:P46" si="1">MAX(M4:O4)</f>
         <v>0.69099999999999995</v>
       </c>
       <c r="Q4" s="2">
@@ -805,7 +805,7 @@
         <v>0.34300000000000003</v>
       </c>
       <c r="T4" s="3">
-        <f>MAX(Q4:S4)</f>
+        <f t="shared" ref="T4:T46" si="2">MAX(Q4:S4)</f>
         <v>0.376</v>
       </c>
     </row>
@@ -841,7 +841,7 @@
         <v>0.60599999999999998</v>
       </c>
       <c r="L5" s="4">
-        <f>MAX(I5:K5)</f>
+        <f t="shared" si="0"/>
         <v>0.77100000000000002</v>
       </c>
       <c r="M5" s="2">
@@ -854,7 +854,7 @@
         <v>0.60499999999999998</v>
       </c>
       <c r="P5" s="4">
-        <f>MAX(M5:O5)</f>
+        <f t="shared" si="1"/>
         <v>0.71399999999999997</v>
       </c>
       <c r="Q5" s="2">
@@ -867,7 +867,7 @@
         <v>0.37</v>
       </c>
       <c r="T5" s="3">
-        <f>MAX(Q5:S5)</f>
+        <f t="shared" si="2"/>
         <v>0.41199999999999998</v>
       </c>
     </row>
@@ -903,7 +903,7 @@
         <v>0.57099999999999995</v>
       </c>
       <c r="L6" s="4">
-        <f>MAX(I6:K6)</f>
+        <f t="shared" si="0"/>
         <v>0.745</v>
       </c>
       <c r="M6" s="2">
@@ -916,7 +916,7 @@
         <v>0.59199999999999997</v>
       </c>
       <c r="P6" s="4">
-        <f>MAX(M6:O6)</f>
+        <f t="shared" si="1"/>
         <v>0.70699999999999996</v>
       </c>
       <c r="Q6" s="2">
@@ -929,7 +929,7 @@
         <v>0.35599999999999998</v>
       </c>
       <c r="T6" s="3">
-        <f>MAX(Q6:S6)</f>
+        <f t="shared" si="2"/>
         <v>0.40899999999999997</v>
       </c>
     </row>
@@ -962,7 +962,7 @@
         <v>0.57299999999999995</v>
       </c>
       <c r="L7" s="4">
-        <f>MAX(I7:K7)</f>
+        <f t="shared" si="0"/>
         <v>0.746</v>
       </c>
       <c r="M7" s="2">
@@ -975,7 +975,7 @@
         <v>0.57899999999999996</v>
       </c>
       <c r="P7" s="4">
-        <f>MAX(M7:O7)</f>
+        <f t="shared" si="1"/>
         <v>0.67700000000000005</v>
       </c>
       <c r="Q7" s="2">
@@ -988,7 +988,7 @@
         <v>0.33800000000000002</v>
       </c>
       <c r="T7" s="3">
-        <f>MAX(Q7:S7)</f>
+        <f t="shared" si="2"/>
         <v>0.373</v>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
         <v>0.57399999999999995</v>
       </c>
       <c r="L8" s="4">
-        <f>MAX(I8:K8)</f>
+        <f t="shared" si="0"/>
         <v>0.752</v>
       </c>
       <c r="M8" s="2">
@@ -1034,7 +1034,7 @@
         <v>0.58499999999999996</v>
       </c>
       <c r="P8" s="4">
-        <f>MAX(M8:O8)</f>
+        <f t="shared" si="1"/>
         <v>0.69099999999999995</v>
       </c>
       <c r="Q8" s="2">
@@ -1047,7 +1047,7 @@
         <v>0.34599999999999997</v>
       </c>
       <c r="T8" s="3">
-        <f>MAX(Q8:S8)</f>
+        <f t="shared" si="2"/>
         <v>0.38400000000000001</v>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
         <v>0.56399999999999995</v>
       </c>
       <c r="L9" s="4">
-        <f>MAX(I9:K9)</f>
+        <f t="shared" si="0"/>
         <v>0.73899999999999999</v>
       </c>
       <c r="M9" s="2">
@@ -1093,7 +1093,7 @@
         <v>0.57499999999999996</v>
       </c>
       <c r="P9" s="4">
-        <f>MAX(M9:O9)</f>
+        <f t="shared" si="1"/>
         <v>0.68200000000000005</v>
       </c>
       <c r="Q9" s="2">
@@ -1106,7 +1106,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="T9" s="3">
-        <f>MAX(Q9:S9)</f>
+        <f t="shared" si="2"/>
         <v>0.371</v>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
         <v>0.58499999999999996</v>
       </c>
       <c r="L10" s="4">
-        <f>MAX(I10:K10)</f>
+        <f t="shared" si="0"/>
         <v>0.76900000000000002</v>
       </c>
       <c r="M10" s="2">
@@ -1152,7 +1152,7 @@
         <v>0.59099999999999997</v>
       </c>
       <c r="P10" s="4">
-        <f>MAX(M10:O10)</f>
+        <f t="shared" si="1"/>
         <v>0.71199999999999997</v>
       </c>
       <c r="Q10" s="2">
@@ -1165,7 +1165,7 @@
         <v>0.36399999999999999</v>
       </c>
       <c r="T10" s="3">
-        <f>MAX(Q10:S10)</f>
+        <f t="shared" si="2"/>
         <v>0.40899999999999997</v>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
         <v>0.58399999999999996</v>
       </c>
       <c r="L11" s="4">
-        <f>MAX(I11:K11)</f>
+        <f t="shared" si="0"/>
         <v>0.76600000000000001</v>
       </c>
       <c r="M11" s="2">
@@ -1211,7 +1211,7 @@
         <v>0.57599999999999996</v>
       </c>
       <c r="P11" s="4">
-        <f>MAX(M11:O11)</f>
+        <f t="shared" si="1"/>
         <v>0.69699999999999995</v>
       </c>
       <c r="Q11" s="2">
@@ -1224,7 +1224,7 @@
         <v>0.34899999999999998</v>
       </c>
       <c r="T11" s="3">
-        <f>MAX(Q11:S11)</f>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
         <v>0.58199999999999996</v>
       </c>
       <c r="L12" s="4">
-        <f>MAX(I12:K12)</f>
+        <f t="shared" si="0"/>
         <v>0.74299999999999999</v>
       </c>
       <c r="M12" s="2">
@@ -1270,7 +1270,7 @@
         <v>0.56499999999999995</v>
       </c>
       <c r="P12" s="4">
-        <f>MAX(M12:O12)</f>
+        <f t="shared" si="1"/>
         <v>0.68200000000000005</v>
       </c>
       <c r="Q12" s="2">
@@ -1283,7 +1283,7 @@
         <v>0.32900000000000001</v>
       </c>
       <c r="T12" s="3">
-        <f>MAX(Q12:S12)</f>
+        <f t="shared" si="2"/>
         <v>0.379</v>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
         <v>0.59899999999999998</v>
       </c>
       <c r="L13" s="4">
-        <f>MAX(I13:K13)</f>
+        <f t="shared" si="0"/>
         <v>0.78500000000000003</v>
       </c>
       <c r="M13" s="2">
@@ -1329,7 +1329,7 @@
         <v>0.60899999999999999</v>
       </c>
       <c r="P13" s="4">
-        <f>MAX(M13:O13)</f>
+        <f t="shared" si="1"/>
         <v>0.73399999999999999</v>
       </c>
       <c r="Q13" s="2">
@@ -1342,7 +1342,7 @@
         <v>0.38200000000000001</v>
       </c>
       <c r="T13" s="3">
-        <f>MAX(Q13:S13)</f>
+        <f t="shared" si="2"/>
         <v>0.442</v>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         <v>0.56599999999999995</v>
       </c>
       <c r="L14" s="4">
-        <f>MAX(I14:K14)</f>
+        <f t="shared" si="0"/>
         <v>0.755</v>
       </c>
       <c r="M14" s="2">
@@ -1388,7 +1388,7 @@
         <v>0.57399999999999995</v>
       </c>
       <c r="P14" s="4">
-        <f>MAX(M14:O14)</f>
+        <f t="shared" si="1"/>
         <v>0.71199999999999997</v>
       </c>
       <c r="Q14" s="2">
@@ -1401,7 +1401,7 @@
         <v>0.34</v>
       </c>
       <c r="T14" s="3">
-        <f>MAX(Q14:S14)</f>
+        <f t="shared" si="2"/>
         <v>0.40200000000000002</v>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
         <v>0.55700000000000005</v>
       </c>
       <c r="L15" s="4">
-        <f>MAX(I15:K15)</f>
+        <f t="shared" si="0"/>
         <v>0.74199999999999999</v>
       </c>
       <c r="M15" s="2">
@@ -1447,7 +1447,7 @@
         <v>0.56200000000000006</v>
       </c>
       <c r="P15" s="4">
-        <f>MAX(M15:O15)</f>
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
       <c r="Q15" s="2">
@@ -1460,7 +1460,7 @@
         <v>0.32800000000000001</v>
       </c>
       <c r="T15" s="3">
-        <f>MAX(Q15:S15)</f>
+        <f t="shared" si="2"/>
         <v>0.39100000000000001</v>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
         <v>0.56899999999999995</v>
       </c>
       <c r="L16" s="4">
-        <f>MAX(I16:K16)</f>
+        <f t="shared" si="0"/>
         <v>0.73799999999999999</v>
       </c>
       <c r="M16" s="2">
@@ -1506,7 +1506,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="P16" s="4">
-        <f>MAX(M16:O16)</f>
+        <f t="shared" si="1"/>
         <v>0.69899999999999995</v>
       </c>
       <c r="Q16" s="2">
@@ -1519,7 +1519,7 @@
         <v>0.33</v>
       </c>
       <c r="T16" s="3">
-        <f>MAX(Q16:S16)</f>
+        <f t="shared" si="2"/>
         <v>0.39100000000000001</v>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
         <v>0.57799999999999996</v>
       </c>
       <c r="L17" s="4">
-        <f>MAX(I17:K17)</f>
+        <f t="shared" si="0"/>
         <v>0.76400000000000001</v>
       </c>
       <c r="M17" s="2">
@@ -1565,7 +1565,7 @@
         <v>0.55700000000000005</v>
       </c>
       <c r="P17" s="4">
-        <f>MAX(M17:O17)</f>
+        <f t="shared" si="1"/>
         <v>0.70199999999999996</v>
       </c>
       <c r="Q17" s="2">
@@ -1578,7 +1578,7 @@
         <v>0.34399999999999997</v>
       </c>
       <c r="T17" s="3">
-        <f>MAX(Q17:S17)</f>
+        <f t="shared" si="2"/>
         <v>0.41099999999999998</v>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
         <v>0.51900000000000002</v>
       </c>
       <c r="L18" s="4">
-        <f>MAX(I18:K18)</f>
+        <f t="shared" si="0"/>
         <v>0.69499999999999995</v>
       </c>
       <c r="M18" s="2">
@@ -1624,7 +1624,7 @@
         <v>0.52</v>
       </c>
       <c r="P18" s="4">
-        <f>MAX(M18:O18)</f>
+        <f t="shared" si="1"/>
         <v>0.65800000000000003</v>
       </c>
       <c r="Q18" s="2">
@@ -1637,7 +1637,7 @@
         <v>0.28399999999999997</v>
       </c>
       <c r="T18" s="3">
-        <f>MAX(Q18:S18)</f>
+        <f t="shared" si="2"/>
         <v>0.33400000000000002</v>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
         <v>0.54100000000000004</v>
       </c>
       <c r="L19" s="4">
-        <f>MAX(I19:K19)</f>
+        <f t="shared" si="0"/>
         <v>0.69299999999999995</v>
       </c>
       <c r="M19" s="2">
@@ -1686,7 +1686,7 @@
         <v>0.61799999999999999</v>
       </c>
       <c r="P19" s="4">
-        <f>MAX(M19:O19)</f>
+        <f t="shared" si="1"/>
         <v>0.72299999999999998</v>
       </c>
       <c r="Q19" s="2">
@@ -1699,7 +1699,7 @@
         <v>0.34200000000000003</v>
       </c>
       <c r="T19" s="3">
-        <f>MAX(Q19:S19)</f>
+        <f t="shared" si="2"/>
         <v>0.36599999999999999</v>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>0.53700000000000003</v>
       </c>
       <c r="L20" s="4">
-        <f>MAX(I20:K20)</f>
+        <f t="shared" si="0"/>
         <v>0.68100000000000005</v>
       </c>
       <c r="M20" s="2">
@@ -1748,7 +1748,7 @@
         <v>0.628</v>
       </c>
       <c r="P20" s="4">
-        <f>MAX(M20:O20)</f>
+        <f t="shared" si="1"/>
         <v>0.73499999999999999</v>
       </c>
       <c r="Q20" s="2">
@@ -1761,7 +1761,7 @@
         <v>0.35199999999999998</v>
       </c>
       <c r="T20" s="3">
-        <f>MAX(Q20:S20)</f>
+        <f t="shared" si="2"/>
         <v>0.376</v>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
         <v>0.54200000000000004</v>
       </c>
       <c r="L21" s="4">
-        <f>MAX(I21:K21)</f>
+        <f t="shared" si="0"/>
         <v>0.68600000000000005</v>
       </c>
       <c r="M21" s="2">
@@ -1810,7 +1810,7 @@
         <v>0.64800000000000002</v>
       </c>
       <c r="P21" s="4">
-        <f>MAX(M21:O21)</f>
+        <f t="shared" si="1"/>
         <v>0.77400000000000002</v>
       </c>
       <c r="Q21" s="2">
@@ -1823,7 +1823,7 @@
         <v>0.40699999999999997</v>
       </c>
       <c r="T21" s="3">
-        <f>MAX(Q21:S21)</f>
+        <f t="shared" si="2"/>
         <v>0.45500000000000002</v>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
         <v>0.58299999999999996</v>
       </c>
       <c r="L22" s="4">
-        <f>MAX(I22:K22)</f>
+        <f t="shared" si="0"/>
         <v>0.58299999999999996</v>
       </c>
       <c r="M22" s="2">
@@ -1869,7 +1869,7 @@
         <v>0.68</v>
       </c>
       <c r="P22" s="4">
-        <f>MAX(M22:O22)</f>
+        <f t="shared" si="1"/>
         <v>0.68</v>
       </c>
       <c r="Q22" s="2">
@@ -1882,7 +1882,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="T22" s="3">
-        <f>MAX(Q22:S22)</f>
+        <f t="shared" si="2"/>
         <v>0.33500000000000002</v>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
         <v>0.64</v>
       </c>
       <c r="L23" s="4">
-        <f>MAX(I23:K23)</f>
+        <f t="shared" si="0"/>
         <v>0.64100000000000001</v>
       </c>
       <c r="M23" s="2">
@@ -1928,7 +1928,7 @@
         <v>0.71099999999999997</v>
       </c>
       <c r="P23" s="4">
-        <f>MAX(M23:O23)</f>
+        <f t="shared" si="1"/>
         <v>0.71099999999999997</v>
       </c>
       <c r="Q23" s="2">
@@ -1941,7 +1941,7 @@
         <v>0.371</v>
       </c>
       <c r="T23" s="3">
-        <f>MAX(Q23:S23)</f>
+        <f t="shared" si="2"/>
         <v>0.371</v>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
         <v>0.64100000000000001</v>
       </c>
       <c r="L24" s="4">
-        <f>MAX(I24:K24)</f>
+        <f t="shared" si="0"/>
         <v>0.64200000000000002</v>
       </c>
       <c r="M24" s="2">
@@ -1987,7 +1987,7 @@
         <v>0.70799999999999996</v>
       </c>
       <c r="P24" s="4">
-        <f>MAX(M24:O24)</f>
+        <f t="shared" si="1"/>
         <v>0.70799999999999996</v>
       </c>
       <c r="Q24" s="2">
@@ -2000,7 +2000,7 @@
         <v>0.373</v>
       </c>
       <c r="T24" s="3">
-        <f>MAX(Q24:S24)</f>
+        <f t="shared" si="2"/>
         <v>0.373</v>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="L25" s="4">
-        <f>MAX(I25:K25)</f>
+        <f t="shared" si="0"/>
         <v>0.56999999999999995</v>
       </c>
       <c r="M25" s="2">
@@ -2046,7 +2046,7 @@
         <v>0.67600000000000005</v>
       </c>
       <c r="P25" s="4">
-        <f>MAX(M25:O25)</f>
+        <f t="shared" si="1"/>
         <v>0.67600000000000005</v>
       </c>
       <c r="Q25" s="2">
@@ -2059,7 +2059,7 @@
         <v>0.35799999999999998</v>
       </c>
       <c r="T25" s="3">
-        <f>MAX(Q25:S25)</f>
+        <f t="shared" si="2"/>
         <v>0.35799999999999998</v>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
         <v>0.54900000000000004</v>
       </c>
       <c r="L26" s="4">
-        <f>MAX(I26:K26)</f>
+        <f t="shared" si="0"/>
         <v>0.54900000000000004</v>
       </c>
       <c r="M26" s="2">
@@ -2105,7 +2105,7 @@
         <v>0.64400000000000002</v>
       </c>
       <c r="P26" s="4">
-        <f>MAX(M26:O26)</f>
+        <f t="shared" si="1"/>
         <v>0.64400000000000002</v>
       </c>
       <c r="Q26" s="2">
@@ -2118,7 +2118,7 @@
         <v>0.33400000000000002</v>
       </c>
       <c r="T26" s="3">
-        <f>MAX(Q26:S26)</f>
+        <f t="shared" si="2"/>
         <v>0.33400000000000002</v>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
         <v>0.629</v>
       </c>
       <c r="L27" s="4">
-        <f>MAX(I27:K27)</f>
+        <f t="shared" si="0"/>
         <v>0.66400000000000003</v>
       </c>
       <c r="M27" s="2">
@@ -2167,7 +2167,7 @@
         <v>0.66200000000000003</v>
       </c>
       <c r="P27" s="4">
-        <f>MAX(M27:O27)</f>
+        <f t="shared" si="1"/>
         <v>0.68100000000000005</v>
       </c>
       <c r="Q27" s="2">
@@ -2180,7 +2180,7 @@
         <v>0.34799999999999998</v>
       </c>
       <c r="T27" s="3">
-        <f>MAX(Q27:S27)</f>
+        <f t="shared" si="2"/>
         <v>0.34899999999999998</v>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
         <v>0.64</v>
       </c>
       <c r="L28" s="4">
-        <f>MAX(I28:K28)</f>
+        <f t="shared" si="0"/>
         <v>0.66800000000000004</v>
       </c>
       <c r="M28" s="2">
@@ -2229,7 +2229,7 @@
         <v>0.65600000000000003</v>
       </c>
       <c r="P28" s="4">
-        <f>MAX(M28:O28)</f>
+        <f t="shared" si="1"/>
         <v>0.68100000000000005</v>
       </c>
       <c r="Q28" s="2">
@@ -2242,7 +2242,7 @@
         <v>0.35</v>
       </c>
       <c r="T28" s="3">
-        <f>MAX(Q28:S28)</f>
+        <f t="shared" si="2"/>
         <v>0.35299999999999998</v>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
         <v>0.58699999999999997</v>
       </c>
       <c r="L29" s="4">
-        <f>MAX(I29:K29)</f>
+        <f t="shared" si="0"/>
         <v>0.60499999999999998</v>
       </c>
       <c r="M29" s="2">
@@ -2291,7 +2291,7 @@
         <v>0.61199999999999999</v>
       </c>
       <c r="P29" s="4">
-        <f>MAX(M29:O29)</f>
+        <f t="shared" si="1"/>
         <v>0.63200000000000001</v>
       </c>
       <c r="Q29" s="2">
@@ -2304,7 +2304,7 @@
         <v>0.33</v>
       </c>
       <c r="T29" s="3">
-        <f>MAX(Q29:S29)</f>
+        <f t="shared" si="2"/>
         <v>0.33400000000000002</v>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
         <v>0.57699999999999996</v>
       </c>
       <c r="L30" s="4">
-        <f>MAX(I30:K30)</f>
+        <f t="shared" si="0"/>
         <v>0.68600000000000005</v>
       </c>
       <c r="M30" s="2">
@@ -2353,7 +2353,7 @@
         <v>0.57699999999999996</v>
       </c>
       <c r="P30" s="4">
-        <f>MAX(M30:O30)</f>
+        <f t="shared" si="1"/>
         <v>0.65100000000000002</v>
       </c>
       <c r="Q30" s="2">
@@ -2366,7 +2366,7 @@
         <v>0.32700000000000001</v>
       </c>
       <c r="T30" s="3">
-        <f>MAX(Q30:S30)</f>
+        <f t="shared" si="2"/>
         <v>0.33700000000000002</v>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="L31" s="4">
-        <f>MAX(I31:K31)</f>
+        <f t="shared" si="0"/>
         <v>0.69399999999999995</v>
       </c>
       <c r="M31" s="2">
@@ -2415,7 +2415,7 @@
         <v>0.57199999999999995</v>
       </c>
       <c r="P31" s="4">
-        <f>MAX(M31:O31)</f>
+        <f t="shared" si="1"/>
         <v>0.65700000000000003</v>
       </c>
       <c r="Q31" s="2">
@@ -2428,7 +2428,7 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="T31" s="3">
-        <f>MAX(Q31:S31)</f>
+        <f t="shared" si="2"/>
         <v>0.35599999999999998</v>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
         <v>0.56899999999999995</v>
       </c>
       <c r="L32" s="4">
-        <f>MAX(I32:K32)</f>
+        <f t="shared" si="0"/>
         <v>0.64900000000000002</v>
       </c>
       <c r="M32" s="2">
@@ -2477,7 +2477,7 @@
         <v>0.53600000000000003</v>
       </c>
       <c r="P32" s="4">
-        <f>MAX(M32:O32)</f>
+        <f t="shared" si="1"/>
         <v>0.61499999999999999</v>
       </c>
       <c r="Q32" s="2">
@@ -2490,7 +2490,7 @@
         <v>0.31</v>
       </c>
       <c r="T32" s="3">
-        <f>MAX(Q32:S32)</f>
+        <f t="shared" si="2"/>
         <v>0.33500000000000002</v>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
         <v>0.53600000000000003</v>
       </c>
       <c r="L33" s="4">
-        <f>MAX(I33:K33)</f>
+        <f t="shared" si="0"/>
         <v>0.53600000000000003</v>
       </c>
       <c r="M33" s="2">
@@ -2539,7 +2539,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="P33" s="4">
-        <f>MAX(M33:O33)</f>
+        <f t="shared" si="1"/>
         <v>0.59499999999999997</v>
       </c>
       <c r="Q33" s="2">
@@ -2552,7 +2552,7 @@
         <v>0.27400000000000002</v>
       </c>
       <c r="T33" s="3">
-        <f>MAX(Q33:S33)</f>
+        <f t="shared" si="2"/>
         <v>0.27400000000000002</v>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
         <v>0.60799999999999998</v>
       </c>
       <c r="L34" s="4">
-        <f>MAX(I34:K34)</f>
+        <f t="shared" si="0"/>
         <v>0.60899999999999999</v>
       </c>
       <c r="M34" s="2">
@@ -2601,7 +2601,7 @@
         <v>0.65700000000000003</v>
       </c>
       <c r="P34" s="4">
-        <f>MAX(M34:O34)</f>
+        <f t="shared" si="1"/>
         <v>0.65700000000000003</v>
       </c>
       <c r="Q34" s="2">
@@ -2614,7 +2614,7 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="T34" s="3">
-        <f>MAX(Q34:S34)</f>
+        <f t="shared" si="2"/>
         <v>0.33300000000000002</v>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>0.54300000000000004</v>
       </c>
       <c r="L35" s="4">
-        <f>MAX(I35:K35)</f>
+        <f t="shared" si="0"/>
         <v>0.54300000000000004</v>
       </c>
       <c r="M35" s="2">
@@ -2663,7 +2663,7 @@
         <v>0.63900000000000001</v>
       </c>
       <c r="P35" s="4">
-        <f>MAX(M35:O35)</f>
+        <f t="shared" si="1"/>
         <v>0.63900000000000001</v>
       </c>
       <c r="Q35" s="2">
@@ -2676,7 +2676,7 @@
         <v>0.33100000000000002</v>
       </c>
       <c r="T35" s="3">
-        <f>MAX(Q35:S35)</f>
+        <f t="shared" si="2"/>
         <v>0.33100000000000002</v>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
         <v>0.60599999999999998</v>
       </c>
       <c r="L36" s="4">
-        <f>MAX(I36:K36)</f>
+        <f t="shared" si="0"/>
         <v>0.60599999999999998</v>
       </c>
       <c r="M36" s="2">
@@ -2722,7 +2722,7 @@
         <v>0.67700000000000005</v>
       </c>
       <c r="P36" s="4">
-        <f>MAX(M36:O36)</f>
+        <f t="shared" si="1"/>
         <v>0.67700000000000005</v>
       </c>
       <c r="Q36" s="2">
@@ -2735,7 +2735,7 @@
         <v>0.33600000000000002</v>
       </c>
       <c r="T36" s="3">
-        <f>MAX(Q36:S36)</f>
+        <f t="shared" si="2"/>
         <v>0.33600000000000002</v>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
         <v>0.64800000000000002</v>
       </c>
       <c r="L37" s="4">
-        <f>MAX(I37:K37)</f>
+        <f t="shared" si="0"/>
         <v>0.65900000000000003</v>
       </c>
       <c r="M37" s="2">
@@ -2781,7 +2781,7 @@
         <v>0.70499999999999996</v>
       </c>
       <c r="P37" s="4">
-        <f>MAX(M37:O37)</f>
+        <f t="shared" si="1"/>
         <v>0.70499999999999996</v>
       </c>
       <c r="Q37" s="2">
@@ -2794,7 +2794,7 @@
         <v>0.378</v>
       </c>
       <c r="T37" s="3">
-        <f>MAX(Q37:S37)</f>
+        <f t="shared" si="2"/>
         <v>0.378</v>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
         <v>0.64</v>
       </c>
       <c r="L38" s="4">
-        <f>MAX(I38:K38)</f>
+        <f t="shared" si="0"/>
         <v>0.64900000000000002</v>
       </c>
       <c r="M38" s="2">
@@ -2840,7 +2840,7 @@
         <v>0.69699999999999995</v>
       </c>
       <c r="P38" s="4">
-        <f>MAX(M38:O38)</f>
+        <f t="shared" si="1"/>
         <v>0.69699999999999995</v>
       </c>
       <c r="Q38" s="2">
@@ -2853,7 +2853,7 @@
         <v>0.36899999999999999</v>
       </c>
       <c r="T38" s="3">
-        <f>MAX(Q38:S38)</f>
+        <f t="shared" si="2"/>
         <v>0.36899999999999999</v>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
         <v>0.60599999999999998</v>
       </c>
       <c r="L39" s="4">
-        <f>MAX(I39:K39)</f>
+        <f t="shared" si="0"/>
         <v>0.65200000000000002</v>
       </c>
       <c r="M39" s="2">
@@ -2899,7 +2899,7 @@
         <v>0.69499999999999995</v>
       </c>
       <c r="P39" s="4">
-        <f>MAX(M39:O39)</f>
+        <f t="shared" si="1"/>
         <v>0.69499999999999995</v>
       </c>
       <c r="Q39" s="2">
@@ -2912,7 +2912,7 @@
         <v>0.38300000000000001</v>
       </c>
       <c r="T39" s="3">
-        <f>MAX(Q39:S39)</f>
+        <f t="shared" si="2"/>
         <v>0.38300000000000001</v>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
         <v>0.57199999999999995</v>
       </c>
       <c r="L40" s="4">
-        <f>MAX(I40:K40)</f>
+        <f t="shared" si="0"/>
         <v>0.61</v>
       </c>
       <c r="M40" s="2">
@@ -2958,7 +2958,7 @@
         <v>0.64300000000000002</v>
       </c>
       <c r="P40" s="4">
-        <f>MAX(M40:O40)</f>
+        <f t="shared" si="1"/>
         <v>0.64300000000000002</v>
       </c>
       <c r="Q40" s="2">
@@ -2971,8 +2971,380 @@
         <v>0.34599999999999997</v>
       </c>
       <c r="T40" s="3">
-        <f>MAX(Q40:S40)</f>
+        <f t="shared" si="2"/>
         <v>0.34599999999999997</v>
+      </c>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B41" s="8">
+        <v>38</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41">
+        <v>128</v>
+      </c>
+      <c r="G41">
+        <v>200</v>
+      </c>
+      <c r="H41" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="9">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="K41" s="2">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="L41" s="4">
+        <f t="shared" si="0"/>
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="M41" s="9">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="N41" s="2">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="O41" s="2">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="P41" s="4">
+        <f t="shared" si="1"/>
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="Q41" s="9">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="R41" s="2">
+        <v>0.34699999999999998</v>
+      </c>
+      <c r="S41" s="2">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="T41" s="3">
+        <f t="shared" si="2"/>
+        <v>0.34799999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B42" s="8">
+        <v>39</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42">
+        <v>256</v>
+      </c>
+      <c r="G42">
+        <v>200</v>
+      </c>
+      <c r="H42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="9">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="J42" s="2">
+        <v>0.68</v>
+      </c>
+      <c r="K42" s="2">
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="L42" s="4">
+        <f t="shared" si="0"/>
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="M42" s="9">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="N42" s="2">
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="O42" s="2">
+        <v>0.66</v>
+      </c>
+      <c r="P42" s="4">
+        <f t="shared" si="1"/>
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="Q42" s="9">
+        <v>0.315</v>
+      </c>
+      <c r="R42" s="2">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="S42" s="2">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="T42" s="3">
+        <f t="shared" si="2"/>
+        <v>0.36899999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B43" s="8">
+        <v>40</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43">
+        <v>512</v>
+      </c>
+      <c r="G43">
+        <v>200</v>
+      </c>
+      <c r="H43" t="s">
+        <v>13</v>
+      </c>
+      <c r="I43" s="9">
+        <v>0.66600000000000004</v>
+      </c>
+      <c r="J43" s="2">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="K43" s="2">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="L43" s="4">
+        <f t="shared" si="0"/>
+        <v>0.66600000000000004</v>
+      </c>
+      <c r="M43" s="9">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="N43" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="O43" s="2">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="P43" s="4">
+        <f t="shared" si="1"/>
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="R43" s="2">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="S43" s="2">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="T43" s="3">
+        <f t="shared" si="2"/>
+        <v>0.38100000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B44" s="8">
+        <v>41</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44">
+        <v>128</v>
+      </c>
+      <c r="G44">
+        <v>200</v>
+      </c>
+      <c r="H44" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="9">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="J44" s="2">
+        <v>0.68</v>
+      </c>
+      <c r="K44" s="2">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="L44" s="4">
+        <f t="shared" si="0"/>
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="M44" s="9">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="N44" s="2">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="O44" s="2">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="P44" s="4">
+        <f t="shared" si="1"/>
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="Q44" s="9">
+        <v>0.317</v>
+      </c>
+      <c r="R44" s="2">
+        <v>0.35699999999999998</v>
+      </c>
+      <c r="S44" s="2">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="T44" s="3">
+        <f t="shared" si="2"/>
+        <v>0.35699999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B45" s="8">
+        <v>42</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45">
+        <v>256</v>
+      </c>
+      <c r="G45">
+        <v>200</v>
+      </c>
+      <c r="H45" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="9">
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="J45" s="2">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="K45" s="2">
+        <v>0.59299999999999997</v>
+      </c>
+      <c r="L45" s="4">
+        <f t="shared" si="0"/>
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="M45" s="9">
+        <v>0.64700000000000002</v>
+      </c>
+      <c r="N45" s="2">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="O45" s="2">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="P45" s="4">
+        <f t="shared" si="1"/>
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="Q45" s="9">
+        <v>0.34</v>
+      </c>
+      <c r="R45" s="2">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="S45" s="2">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="T45" s="3">
+        <f t="shared" si="2"/>
+        <v>0.36499999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B46" s="8">
+        <v>43</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46">
+        <v>512</v>
+      </c>
+      <c r="G46">
+        <v>200</v>
+      </c>
+      <c r="H46" t="s">
+        <v>13</v>
+      </c>
+      <c r="I46" s="9">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="J46" s="2">
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="K46" s="2">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="L46" s="4">
+        <f t="shared" si="0"/>
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="M46" s="9">
+        <v>0.66200000000000003</v>
+      </c>
+      <c r="N46" s="2">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="O46" s="2">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="P46" s="4">
+        <f t="shared" si="1"/>
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="Q46" s="9">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="R46" s="2">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="S46" s="2">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="T46" s="3">
+        <f t="shared" si="2"/>
+        <v>0.38900000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2987,8 +3359,8 @@
     <mergeCell ref="Q2:T2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="I4:P40">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="J41:L46 I4:P40 N41:P46">
+    <cfRule type="colorScale" priority="359">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2999,8 +3371,44 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:T40">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="R41:T46 Q4:T40">
+    <cfRule type="colorScale" priority="366">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:L46">
+    <cfRule type="colorScale" priority="425">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4:P46">
+    <cfRule type="colorScale" priority="427">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q4:T46">
+    <cfRule type="colorScale" priority="429">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3017,7 +3425,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A847D131-318D-4B5F-8441-AA6E1D149AFA}">
-  <dimension ref="B2:T40"/>
+  <dimension ref="B2:T46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4.28515625" customWidth="1"/>
@@ -3136,7 +3544,7 @@
         <v>0.32200000000000001</v>
       </c>
       <c r="L4" s="3">
-        <f>MAX(I4:K4)</f>
+        <f t="shared" ref="L4:L46" si="0">MAX(I4:K4)</f>
         <v>0.45100000000000001</v>
       </c>
       <c r="M4" s="20">
@@ -3149,7 +3557,7 @@
         <v>0.307</v>
       </c>
       <c r="P4" s="3">
-        <f>MAX(M4:O4)</f>
+        <f t="shared" ref="P4:P46" si="1">MAX(M4:O4)</f>
         <v>0.38300000000000001</v>
       </c>
       <c r="Q4" s="20">
@@ -3162,7 +3570,7 @@
         <v>0.20599999999999999</v>
       </c>
       <c r="T4" s="3">
-        <f>MAX(Q4:S4)</f>
+        <f t="shared" ref="T4:T46" si="2">MAX(Q4:S4)</f>
         <v>0.22900000000000001</v>
       </c>
     </row>
@@ -3198,7 +3606,7 @@
         <v>0.35199999999999998</v>
       </c>
       <c r="L5" s="3">
-        <f>MAX(I5:K5)</f>
+        <f t="shared" si="0"/>
         <v>0.48599999999999999</v>
       </c>
       <c r="M5" s="20">
@@ -3211,7 +3619,7 @@
         <v>0.33100000000000002</v>
       </c>
       <c r="P5" s="3">
-        <f>MAX(M5:O5)</f>
+        <f t="shared" si="1"/>
         <v>0.39500000000000002</v>
       </c>
       <c r="Q5" s="20">
@@ -3224,7 +3632,7 @@
         <v>0.23</v>
       </c>
       <c r="T5" s="3">
-        <f>MAX(Q5:S5)</f>
+        <f t="shared" si="2"/>
         <v>0.23899999999999999</v>
       </c>
     </row>
@@ -3260,7 +3668,7 @@
         <v>0.318</v>
       </c>
       <c r="L6" s="3">
-        <f>MAX(I6:K6)</f>
+        <f t="shared" si="0"/>
         <v>0.48</v>
       </c>
       <c r="M6" s="20">
@@ -3273,7 +3681,7 @@
         <v>0.33100000000000002</v>
       </c>
       <c r="P6" s="3">
-        <f>MAX(M6:O6)</f>
+        <f t="shared" si="1"/>
         <v>0.41799999999999998</v>
       </c>
       <c r="Q6" s="20">
@@ -3286,7 +3694,7 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="T6" s="3">
-        <f>MAX(Q6:S6)</f>
+        <f t="shared" si="2"/>
         <v>0.248</v>
       </c>
     </row>
@@ -3319,7 +3727,7 @@
         <v>0.29799999999999999</v>
       </c>
       <c r="L7" s="3">
-        <f>MAX(I7:K7)</f>
+        <f t="shared" si="0"/>
         <v>0.47399999999999998</v>
       </c>
       <c r="M7" s="20">
@@ -3332,7 +3740,7 @@
         <v>0.309</v>
       </c>
       <c r="P7" s="3">
-        <f>MAX(M7:O7)</f>
+        <f t="shared" si="1"/>
         <v>0.38800000000000001</v>
       </c>
       <c r="Q7" s="20">
@@ -3345,7 +3753,7 @@
         <v>0.20799999999999999</v>
       </c>
       <c r="T7" s="3">
-        <f>MAX(Q7:S7)</f>
+        <f t="shared" si="2"/>
         <v>0.23400000000000001</v>
       </c>
     </row>
@@ -3378,7 +3786,7 @@
         <v>0.33400000000000002</v>
       </c>
       <c r="L8" s="3">
-        <f>MAX(I8:K8)</f>
+        <f t="shared" si="0"/>
         <v>0.48899999999999999</v>
       </c>
       <c r="M8" s="20">
@@ -3391,7 +3799,7 @@
         <v>0.32900000000000001</v>
       </c>
       <c r="P8" s="3">
-        <f>MAX(M8:O8)</f>
+        <f t="shared" si="1"/>
         <v>0.40799999999999997</v>
       </c>
       <c r="Q8" s="20">
@@ -3404,7 +3812,7 @@
         <v>0.222</v>
       </c>
       <c r="T8" s="3">
-        <f>MAX(Q8:S8)</f>
+        <f t="shared" si="2"/>
         <v>0.248</v>
       </c>
     </row>
@@ -3437,7 +3845,7 @@
         <v>0.313</v>
       </c>
       <c r="L9" s="3">
-        <f>MAX(I9:K9)</f>
+        <f t="shared" si="0"/>
         <v>0.46</v>
       </c>
       <c r="M9" s="20">
@@ -3450,7 +3858,7 @@
         <v>0.316</v>
       </c>
       <c r="P9" s="3">
-        <f>MAX(M9:O9)</f>
+        <f t="shared" si="1"/>
         <v>0.39</v>
       </c>
       <c r="Q9" s="20">
@@ -3463,7 +3871,7 @@
         <v>0.21199999999999999</v>
       </c>
       <c r="T9" s="3">
-        <f>MAX(Q9:S9)</f>
+        <f t="shared" si="2"/>
         <v>0.23599999999999999</v>
       </c>
     </row>
@@ -3496,7 +3904,7 @@
         <v>0.32800000000000001</v>
       </c>
       <c r="L10" s="3">
-        <f>MAX(I10:K10)</f>
+        <f t="shared" si="0"/>
         <v>0.48899999999999999</v>
       </c>
       <c r="M10" s="20">
@@ -3509,7 +3917,7 @@
         <v>0.33</v>
       </c>
       <c r="P10" s="3">
-        <f>MAX(M10:O10)</f>
+        <f t="shared" si="1"/>
         <v>0.41299999999999998</v>
       </c>
       <c r="Q10" s="20">
@@ -3522,7 +3930,7 @@
         <v>0.22500000000000001</v>
       </c>
       <c r="T10" s="3">
-        <f>MAX(Q10:S10)</f>
+        <f t="shared" si="2"/>
         <v>0.254</v>
       </c>
     </row>
@@ -3555,7 +3963,7 @@
         <v>0.34</v>
       </c>
       <c r="L11" s="3">
-        <f>MAX(I11:K11)</f>
+        <f t="shared" si="0"/>
         <v>0.48699999999999999</v>
       </c>
       <c r="M11" s="20">
@@ -3568,7 +3976,7 @@
         <v>0.33200000000000002</v>
       </c>
       <c r="P11" s="3">
-        <f>MAX(M11:O11)</f>
+        <f t="shared" si="1"/>
         <v>0.40899999999999997</v>
       </c>
       <c r="Q11" s="20">
@@ -3581,7 +3989,7 @@
         <v>0.222</v>
       </c>
       <c r="T11" s="3">
-        <f>MAX(Q11:S11)</f>
+        <f t="shared" si="2"/>
         <v>0.247</v>
       </c>
     </row>
@@ -3614,7 +4022,7 @@
         <v>0.34799999999999998</v>
       </c>
       <c r="L12" s="3">
-        <f>MAX(I12:K12)</f>
+        <f t="shared" si="0"/>
         <v>0.46700000000000003</v>
       </c>
       <c r="M12" s="20">
@@ -3627,7 +4035,7 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="P12" s="3">
-        <f>MAX(M12:O12)</f>
+        <f t="shared" si="1"/>
         <v>0.38600000000000001</v>
       </c>
       <c r="Q12" s="20">
@@ -3640,7 +4048,7 @@
         <v>0.21199999999999999</v>
       </c>
       <c r="T12" s="3">
-        <f>MAX(Q12:S12)</f>
+        <f t="shared" si="2"/>
         <v>0.23300000000000001</v>
       </c>
     </row>
@@ -3673,7 +4081,7 @@
         <v>0.34799999999999998</v>
       </c>
       <c r="L13" s="3">
-        <f>MAX(I13:K13)</f>
+        <f t="shared" si="0"/>
         <v>0.52500000000000002</v>
       </c>
       <c r="M13" s="20">
@@ -3686,7 +4094,7 @@
         <v>0.34100000000000003</v>
       </c>
       <c r="P13" s="3">
-        <f>MAX(M13:O13)</f>
+        <f t="shared" si="1"/>
         <v>0.44400000000000001</v>
       </c>
       <c r="Q13" s="20">
@@ -3699,7 +4107,7 @@
         <v>0.23400000000000001</v>
       </c>
       <c r="T13" s="3">
-        <f>MAX(Q13:S13)</f>
+        <f t="shared" si="2"/>
         <v>0.26800000000000002</v>
       </c>
     </row>
@@ -3732,7 +4140,7 @@
         <v>0.35499999999999998</v>
       </c>
       <c r="L14" s="3">
-        <f>MAX(I14:K14)</f>
+        <f t="shared" si="0"/>
         <v>0.49299999999999999</v>
       </c>
       <c r="M14" s="20">
@@ -3745,7 +4153,7 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="P14" s="3">
-        <f>MAX(M14:O14)</f>
+        <f t="shared" si="1"/>
         <v>0.40300000000000002</v>
       </c>
       <c r="Q14" s="20">
@@ -3758,7 +4166,7 @@
         <v>0.23200000000000001</v>
       </c>
       <c r="T14" s="3">
-        <f>MAX(Q14:S14)</f>
+        <f t="shared" si="2"/>
         <v>0.251</v>
       </c>
     </row>
@@ -3791,7 +4199,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="L15" s="3">
-        <f>MAX(I15:K15)</f>
+        <f t="shared" si="0"/>
         <v>0.47299999999999998</v>
       </c>
       <c r="M15" s="20">
@@ -3804,7 +4212,7 @@
         <v>0.32100000000000001</v>
       </c>
       <c r="P15" s="3">
-        <f>MAX(M15:O15)</f>
+        <f t="shared" si="1"/>
         <v>0.39</v>
       </c>
       <c r="Q15" s="20">
@@ -3817,7 +4225,7 @@
         <v>0.218</v>
       </c>
       <c r="T15" s="3">
-        <f>MAX(Q15:S15)</f>
+        <f t="shared" si="2"/>
         <v>0.23799999999999999</v>
       </c>
     </row>
@@ -3850,7 +4258,7 @@
         <v>0.32900000000000001</v>
       </c>
       <c r="L16" s="3">
-        <f>MAX(I16:K16)</f>
+        <f t="shared" si="0"/>
         <v>0.47199999999999998</v>
       </c>
       <c r="M16" s="20">
@@ -3863,7 +4271,7 @@
         <v>0.31900000000000001</v>
       </c>
       <c r="P16" s="3">
-        <f>MAX(M16:O16)</f>
+        <f t="shared" si="1"/>
         <v>0.39</v>
       </c>
       <c r="Q16" s="20">
@@ -3876,7 +4284,7 @@
         <v>0.217</v>
       </c>
       <c r="T16" s="3">
-        <f>MAX(Q16:S16)</f>
+        <f t="shared" si="2"/>
         <v>0.23799999999999999</v>
       </c>
     </row>
@@ -3909,7 +4317,7 @@
         <v>0.34100000000000003</v>
       </c>
       <c r="L17" s="3">
-        <f>MAX(I17:K17)</f>
+        <f t="shared" si="0"/>
         <v>0.497</v>
       </c>
       <c r="M17" s="20">
@@ -3922,7 +4330,7 @@
         <v>0.30599999999999999</v>
       </c>
       <c r="P17" s="3">
-        <f>MAX(M17:O17)</f>
+        <f t="shared" si="1"/>
         <v>0.40899999999999997</v>
       </c>
       <c r="Q17" s="20">
@@ -3935,7 +4343,7 @@
         <v>0.218</v>
       </c>
       <c r="T17" s="3">
-        <f>MAX(Q17:S17)</f>
+        <f t="shared" si="2"/>
         <v>0.249</v>
       </c>
     </row>
@@ -3968,7 +4376,7 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="L18" s="3">
-        <f>MAX(I18:K18)</f>
+        <f t="shared" si="0"/>
         <v>0.42799999999999999</v>
       </c>
       <c r="M18" s="20">
@@ -3981,7 +4389,7 @@
         <v>0.3</v>
       </c>
       <c r="P18" s="3">
-        <f>MAX(M18:O18)</f>
+        <f t="shared" si="1"/>
         <v>0.34599999999999997</v>
       </c>
       <c r="Q18" s="20">
@@ -3994,7 +4402,7 @@
         <v>0.19900000000000001</v>
       </c>
       <c r="T18" s="3">
-        <f>MAX(Q18:S18)</f>
+        <f t="shared" si="2"/>
         <v>0.214</v>
       </c>
     </row>
@@ -4030,7 +4438,7 @@
         <v>0.68799999999999994</v>
       </c>
       <c r="L19" s="3">
-        <f>MAX(I19:K19)</f>
+        <f t="shared" si="0"/>
         <v>0.83399999999999996</v>
       </c>
       <c r="M19" s="20">
@@ -4043,7 +4451,7 @@
         <v>0.68</v>
       </c>
       <c r="P19" s="3">
-        <f>MAX(M19:O19)</f>
+        <f t="shared" si="1"/>
         <v>0.75700000000000001</v>
       </c>
       <c r="Q19" s="20">
@@ -4056,7 +4464,7 @@
         <v>0.51500000000000001</v>
       </c>
       <c r="T19" s="3">
-        <f>MAX(Q19:S19)</f>
+        <f t="shared" si="2"/>
         <v>0.55500000000000005</v>
       </c>
     </row>
@@ -4092,7 +4500,7 @@
         <v>0.72399999999999998</v>
       </c>
       <c r="L20" s="3">
-        <f>MAX(I20:K20)</f>
+        <f t="shared" si="0"/>
         <v>0.85899999999999999</v>
       </c>
       <c r="M20" s="20">
@@ -4105,7 +4513,7 @@
         <v>0.70099999999999996</v>
       </c>
       <c r="P20" s="3">
-        <f>MAX(M20:O20)</f>
+        <f t="shared" si="1"/>
         <v>0.77500000000000002</v>
       </c>
       <c r="Q20" s="20">
@@ -4118,7 +4526,7 @@
         <v>0.55700000000000005</v>
       </c>
       <c r="T20" s="3">
-        <f>MAX(Q20:S20)</f>
+        <f t="shared" si="2"/>
         <v>0.58199999999999996</v>
       </c>
     </row>
@@ -4154,7 +4562,7 @@
         <v>0.71699999999999997</v>
       </c>
       <c r="L21" s="3">
-        <f>MAX(I21:K21)</f>
+        <f t="shared" si="0"/>
         <v>0.86299999999999999</v>
       </c>
       <c r="M21" s="20">
@@ -4167,7 +4575,7 @@
         <v>0.69099999999999995</v>
       </c>
       <c r="P21" s="3">
-        <f>MAX(M21:O21)</f>
+        <f t="shared" si="1"/>
         <v>0.78</v>
       </c>
       <c r="Q21" s="20">
@@ -4180,7 +4588,7 @@
         <v>0.55900000000000005</v>
       </c>
       <c r="T21" s="3">
-        <f>MAX(Q21:S21)</f>
+        <f t="shared" si="2"/>
         <v>0.59</v>
       </c>
     </row>
@@ -4213,7 +4621,7 @@
         <v>0.24</v>
       </c>
       <c r="L22" s="3">
-        <f>MAX(I22:K22)</f>
+        <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
       <c r="M22" s="20">
@@ -4226,7 +4634,7 @@
         <v>0.38400000000000001</v>
       </c>
       <c r="P22" s="3">
-        <f>MAX(M22:O22)</f>
+        <f t="shared" si="1"/>
         <v>0.38400000000000001</v>
       </c>
       <c r="Q22" s="20">
@@ -4239,7 +4647,7 @@
         <v>0.20799999999999999</v>
       </c>
       <c r="T22" s="3">
-        <f>MAX(Q22:S22)</f>
+        <f t="shared" si="2"/>
         <v>0.20799999999999999</v>
       </c>
     </row>
@@ -4272,7 +4680,7 @@
         <v>0.33100000000000002</v>
       </c>
       <c r="L23" s="3">
-        <f>MAX(I23:K23)</f>
+        <f t="shared" si="0"/>
         <v>0.33200000000000002</v>
       </c>
       <c r="M23" s="20">
@@ -4285,7 +4693,7 @@
         <v>0.42099999999999999</v>
       </c>
       <c r="P23" s="3">
-        <f>MAX(M23:O23)</f>
+        <f t="shared" si="1"/>
         <v>0.42099999999999999</v>
       </c>
       <c r="Q23" s="20">
@@ -4298,7 +4706,7 @@
         <v>0.23599999999999999</v>
       </c>
       <c r="T23" s="3">
-        <f>MAX(Q23:S23)</f>
+        <f t="shared" si="2"/>
         <v>0.23599999999999999</v>
       </c>
     </row>
@@ -4331,7 +4739,7 @@
         <v>0.33400000000000002</v>
       </c>
       <c r="L24" s="3">
-        <f>MAX(I24:K24)</f>
+        <f t="shared" si="0"/>
         <v>0.33500000000000002</v>
       </c>
       <c r="M24" s="20">
@@ -4344,7 +4752,7 @@
         <v>0.42</v>
       </c>
       <c r="P24" s="3">
-        <f>MAX(M24:O24)</f>
+        <f t="shared" si="1"/>
         <v>0.42</v>
       </c>
       <c r="Q24" s="20">
@@ -4357,7 +4765,7 @@
         <v>0.23499999999999999</v>
       </c>
       <c r="T24" s="3">
-        <f>MAX(Q24:S24)</f>
+        <f t="shared" si="2"/>
         <v>0.23499999999999999</v>
       </c>
     </row>
@@ -4390,7 +4798,7 @@
         <v>0.30099999999999999</v>
       </c>
       <c r="L25" s="3">
-        <f>MAX(I25:K25)</f>
+        <f t="shared" si="0"/>
         <v>0.30099999999999999</v>
       </c>
       <c r="M25" s="20">
@@ -4403,7 +4811,7 @@
         <v>0.42299999999999999</v>
       </c>
       <c r="P25" s="3">
-        <f>MAX(M25:O25)</f>
+        <f t="shared" si="1"/>
         <v>0.42299999999999999</v>
       </c>
       <c r="Q25" s="20">
@@ -4416,7 +4824,7 @@
         <v>0.24399999999999999</v>
       </c>
       <c r="T25" s="3">
-        <f>MAX(Q25:S25)</f>
+        <f t="shared" si="2"/>
         <v>0.24399999999999999</v>
       </c>
     </row>
@@ -4449,7 +4857,7 @@
         <v>0.28100000000000003</v>
       </c>
       <c r="L26" s="3">
-        <f>MAX(I26:K26)</f>
+        <f t="shared" si="0"/>
         <v>0.28100000000000003</v>
       </c>
       <c r="M26" s="20">
@@ -4462,7 +4870,7 @@
         <v>0.38600000000000001</v>
       </c>
       <c r="P26" s="3">
-        <f>MAX(M26:O26)</f>
+        <f t="shared" si="1"/>
         <v>0.38600000000000001</v>
       </c>
       <c r="Q26" s="20">
@@ -4475,7 +4883,7 @@
         <v>0.222</v>
       </c>
       <c r="T26" s="3">
-        <f>MAX(Q26:S26)</f>
+        <f t="shared" si="2"/>
         <v>0.222</v>
       </c>
     </row>
@@ -4511,7 +4919,7 @@
         <v>0.29599999999999999</v>
       </c>
       <c r="L27" s="3">
-        <f>MAX(I27:K27)</f>
+        <f t="shared" si="0"/>
         <v>0.313</v>
       </c>
       <c r="M27" s="20">
@@ -4524,7 +4932,7 @@
         <v>0.376</v>
       </c>
       <c r="P27" s="3">
-        <f>MAX(M27:O27)</f>
+        <f t="shared" si="1"/>
         <v>0.376</v>
       </c>
       <c r="Q27" s="20">
@@ -4537,7 +4945,7 @@
         <v>0.20899999999999999</v>
       </c>
       <c r="T27" s="3">
-        <f>MAX(Q27:S27)</f>
+        <f t="shared" si="2"/>
         <v>0.20899999999999999</v>
       </c>
     </row>
@@ -4573,7 +4981,7 @@
         <v>0.34300000000000003</v>
       </c>
       <c r="L28" s="3">
-        <f>MAX(I28:K28)</f>
+        <f t="shared" si="0"/>
         <v>0.35199999999999998</v>
       </c>
       <c r="M28" s="20">
@@ -4586,7 +4994,7 @@
         <v>0.39300000000000002</v>
       </c>
       <c r="P28" s="3">
-        <f>MAX(M28:O28)</f>
+        <f t="shared" si="1"/>
         <v>0.39900000000000002</v>
       </c>
       <c r="Q28" s="20">
@@ -4599,7 +5007,7 @@
         <v>0.22600000000000001</v>
       </c>
       <c r="T28" s="3">
-        <f>MAX(Q28:S28)</f>
+        <f t="shared" si="2"/>
         <v>0.22600000000000001</v>
       </c>
     </row>
@@ -4635,7 +5043,7 @@
         <v>0.30099999999999999</v>
       </c>
       <c r="L29" s="3">
-        <f>MAX(I29:K29)</f>
+        <f t="shared" si="0"/>
         <v>0.30499999999999999</v>
       </c>
       <c r="M29" s="20">
@@ -4648,7 +5056,7 @@
         <v>0.372</v>
       </c>
       <c r="P29" s="3">
-        <f>MAX(M29:O29)</f>
+        <f t="shared" si="1"/>
         <v>0.376</v>
       </c>
       <c r="Q29" s="20">
@@ -4661,7 +5069,7 @@
         <v>0.216</v>
       </c>
       <c r="T29" s="3">
-        <f>MAX(Q29:S29)</f>
+        <f t="shared" si="2"/>
         <v>0.216</v>
       </c>
     </row>
@@ -4697,7 +5105,7 @@
         <v>0.29299999999999998</v>
       </c>
       <c r="L30" s="3">
-        <f>MAX(I30:K30)</f>
+        <f t="shared" si="0"/>
         <v>0.34899999999999998</v>
       </c>
       <c r="M30" s="20">
@@ -4710,7 +5118,7 @@
         <v>0.34499999999999997</v>
       </c>
       <c r="P30" s="3">
-        <f>MAX(M30:O30)</f>
+        <f t="shared" si="1"/>
         <v>0.371</v>
       </c>
       <c r="Q30" s="20">
@@ -4723,7 +5131,7 @@
         <v>0.20399999999999999</v>
       </c>
       <c r="T30" s="3">
-        <f>MAX(Q30:S30)</f>
+        <f t="shared" si="2"/>
         <v>0.20399999999999999</v>
       </c>
     </row>
@@ -4759,7 +5167,7 @@
         <v>0.33600000000000002</v>
       </c>
       <c r="L31" s="3">
-        <f>MAX(I31:K31)</f>
+        <f t="shared" si="0"/>
         <v>0.372</v>
       </c>
       <c r="M31" s="20">
@@ -4772,7 +5180,7 @@
         <v>0.35599999999999998</v>
       </c>
       <c r="P31" s="3">
-        <f>MAX(M31:O31)</f>
+        <f t="shared" si="1"/>
         <v>0.39100000000000001</v>
       </c>
       <c r="Q31" s="20">
@@ -4785,7 +5193,7 @@
         <v>0.22</v>
       </c>
       <c r="T31" s="3">
-        <f>MAX(Q31:S31)</f>
+        <f t="shared" si="2"/>
         <v>0.22700000000000001</v>
       </c>
     </row>
@@ -4821,7 +5229,7 @@
         <v>0.29499999999999998</v>
       </c>
       <c r="L32" s="3">
-        <f>MAX(I32:K32)</f>
+        <f t="shared" si="0"/>
         <v>0.32500000000000001</v>
       </c>
       <c r="M32" s="20">
@@ -4834,7 +5242,7 @@
         <v>0.33</v>
       </c>
       <c r="P32" s="3">
-        <f>MAX(M32:O32)</f>
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
       <c r="Q32" s="20">
@@ -4847,7 +5255,7 @@
         <v>0.20799999999999999</v>
       </c>
       <c r="T32" s="3">
-        <f>MAX(Q32:S32)</f>
+        <f t="shared" si="2"/>
         <v>0.217</v>
       </c>
     </row>
@@ -4883,7 +5291,7 @@
         <v>0.186</v>
       </c>
       <c r="L33" s="3">
-        <f>MAX(I33:K33)</f>
+        <f t="shared" si="0"/>
         <v>0.186</v>
       </c>
       <c r="M33" s="20">
@@ -4896,7 +5304,7 @@
         <v>0.26100000000000001</v>
       </c>
       <c r="P33" s="3">
-        <f>MAX(M33:O33)</f>
+        <f t="shared" si="1"/>
         <v>0.26100000000000001</v>
       </c>
       <c r="Q33" s="20">
@@ -4909,7 +5317,7 @@
         <v>0.13900000000000001</v>
       </c>
       <c r="T33" s="3">
-        <f>MAX(Q33:S33)</f>
+        <f t="shared" si="2"/>
         <v>0.13900000000000001</v>
       </c>
     </row>
@@ -4945,7 +5353,7 @@
         <v>0.311</v>
       </c>
       <c r="L34" s="3">
-        <f>MAX(I34:K34)</f>
+        <f t="shared" si="0"/>
         <v>0.311</v>
       </c>
       <c r="M34" s="20">
@@ -4958,7 +5366,7 @@
         <v>0.36599999999999999</v>
       </c>
       <c r="P34" s="3">
-        <f>MAX(M34:O34)</f>
+        <f t="shared" si="1"/>
         <v>0.36599999999999999</v>
       </c>
       <c r="Q34" s="20">
@@ -4971,7 +5379,7 @@
         <v>0.20699999999999999</v>
       </c>
       <c r="T34" s="3">
-        <f>MAX(Q34:S34)</f>
+        <f t="shared" si="2"/>
         <v>0.20699999999999999</v>
       </c>
     </row>
@@ -5007,7 +5415,7 @@
         <v>0.28299999999999997</v>
       </c>
       <c r="L35" s="3">
-        <f>MAX(I35:K35)</f>
+        <f t="shared" si="0"/>
         <v>0.28299999999999997</v>
       </c>
       <c r="M35" s="20">
@@ -5020,7 +5428,7 @@
         <v>0.38200000000000001</v>
       </c>
       <c r="P35" s="3">
-        <f>MAX(M35:O35)</f>
+        <f t="shared" si="1"/>
         <v>0.38200000000000001</v>
       </c>
       <c r="Q35" s="20">
@@ -5033,7 +5441,7 @@
         <v>0.215</v>
       </c>
       <c r="T35" s="3">
-        <f>MAX(Q35:S35)</f>
+        <f t="shared" si="2"/>
         <v>0.215</v>
       </c>
     </row>
@@ -5066,7 +5474,7 @@
         <v>0.25</v>
       </c>
       <c r="L36" s="3">
-        <f>MAX(I36:K36)</f>
+        <f t="shared" si="0"/>
         <v>0.254</v>
       </c>
       <c r="M36" s="20">
@@ -5079,7 +5487,7 @@
         <v>0.35</v>
       </c>
       <c r="P36" s="3">
-        <f>MAX(M36:O36)</f>
+        <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
       <c r="Q36" s="20">
@@ -5092,7 +5500,7 @@
         <v>0.182</v>
       </c>
       <c r="T36" s="3">
-        <f>MAX(Q36:S36)</f>
+        <f t="shared" si="2"/>
         <v>0.182</v>
       </c>
     </row>
@@ -5125,7 +5533,7 @@
         <v>0.32900000000000001</v>
       </c>
       <c r="L37" s="3">
-        <f>MAX(I37:K37)</f>
+        <f t="shared" si="0"/>
         <v>0.33400000000000002</v>
       </c>
       <c r="M37" s="20">
@@ -5138,7 +5546,7 @@
         <v>0.39900000000000002</v>
       </c>
       <c r="P37" s="3">
-        <f>MAX(M37:O37)</f>
+        <f t="shared" si="1"/>
         <v>0.39900000000000002</v>
       </c>
       <c r="Q37" s="20">
@@ -5151,7 +5559,7 @@
         <v>0.219</v>
       </c>
       <c r="T37" s="3">
-        <f>MAX(Q37:S37)</f>
+        <f t="shared" si="2"/>
         <v>0.219</v>
       </c>
     </row>
@@ -5184,7 +5592,7 @@
         <v>0.33700000000000002</v>
       </c>
       <c r="L38" s="3">
-        <f>MAX(I38:K38)</f>
+        <f t="shared" si="0"/>
         <v>0.33900000000000002</v>
       </c>
       <c r="M38" s="20">
@@ -5197,7 +5605,7 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="P38" s="3">
-        <f>MAX(M38:O38)</f>
+        <f t="shared" si="1"/>
         <v>0.40899999999999997</v>
       </c>
       <c r="Q38" s="20">
@@ -5210,7 +5618,7 @@
         <v>0.22900000000000001</v>
       </c>
       <c r="T38" s="3">
-        <f>MAX(Q38:S38)</f>
+        <f t="shared" si="2"/>
         <v>0.22900000000000001</v>
       </c>
     </row>
@@ -5243,7 +5651,7 @@
         <v>0.33100000000000002</v>
       </c>
       <c r="L39" s="3">
-        <f>MAX(I39:K39)</f>
+        <f t="shared" si="0"/>
         <v>0.35099999999999998</v>
       </c>
       <c r="M39" s="20">
@@ -5256,7 +5664,7 @@
         <v>0.38700000000000001</v>
       </c>
       <c r="P39" s="3">
-        <f>MAX(M39:O39)</f>
+        <f t="shared" si="1"/>
         <v>0.38700000000000001</v>
       </c>
       <c r="Q39" s="20">
@@ -5269,7 +5677,7 @@
         <v>0.219</v>
       </c>
       <c r="T39" s="3">
-        <f>MAX(Q39:S39)</f>
+        <f t="shared" si="2"/>
         <v>0.219</v>
       </c>
     </row>
@@ -5302,7 +5710,7 @@
         <v>0.29099999999999998</v>
       </c>
       <c r="L40" s="3">
-        <f>MAX(I40:K40)</f>
+        <f t="shared" si="0"/>
         <v>0.30399999999999999</v>
       </c>
       <c r="M40" s="20">
@@ -5315,7 +5723,7 @@
         <v>0.34599999999999997</v>
       </c>
       <c r="P40" s="3">
-        <f>MAX(M40:O40)</f>
+        <f t="shared" si="1"/>
         <v>0.34599999999999997</v>
       </c>
       <c r="Q40" s="20">
@@ -5328,8 +5736,380 @@
         <v>0.191</v>
       </c>
       <c r="T40" s="3">
-        <f>MAX(Q40:S40)</f>
+        <f t="shared" si="2"/>
         <v>0.191</v>
+      </c>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B41" s="1">
+        <v>38</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41">
+        <v>128</v>
+      </c>
+      <c r="G41">
+        <v>200</v>
+      </c>
+      <c r="H41" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="9">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="K41" s="2">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="L41" s="3">
+        <f t="shared" si="0"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M41" s="9">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="N41" s="2">
+        <v>0.34200000000000003</v>
+      </c>
+      <c r="O41" s="2">
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="P41" s="3">
+        <f t="shared" si="1"/>
+        <v>0.38200000000000001</v>
+      </c>
+      <c r="Q41" s="9">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="R41" s="2">
+        <v>0.184</v>
+      </c>
+      <c r="S41" s="2">
+        <v>0.214</v>
+      </c>
+      <c r="T41" s="3">
+        <f t="shared" si="2"/>
+        <v>0.214</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B42" s="1">
+        <v>39</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42">
+        <v>256</v>
+      </c>
+      <c r="G42">
+        <v>200</v>
+      </c>
+      <c r="H42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="9">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="J42" s="2">
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="K42" s="2">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="L42" s="3">
+        <f t="shared" si="0"/>
+        <v>0.36499999999999999</v>
+      </c>
+      <c r="M42" s="9">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="N42" s="2">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="O42" s="2">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="P42" s="3">
+        <f t="shared" si="1"/>
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="Q42" s="9">
+        <v>0.182</v>
+      </c>
+      <c r="R42" s="2">
+        <v>0.218</v>
+      </c>
+      <c r="S42" s="2">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="T42" s="3">
+        <f t="shared" si="2"/>
+        <v>0.23599999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B43" s="1">
+        <v>40</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43">
+        <v>512</v>
+      </c>
+      <c r="G43">
+        <v>200</v>
+      </c>
+      <c r="H43" t="s">
+        <v>13</v>
+      </c>
+      <c r="I43" s="9">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="J43" s="2">
+        <v>0.32</v>
+      </c>
+      <c r="K43" s="2">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="L43" s="3">
+        <f t="shared" si="0"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M43" s="9">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="N43" s="2">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="O43" s="2">
+        <v>0.374</v>
+      </c>
+      <c r="P43" s="3">
+        <f t="shared" si="1"/>
+        <v>0.374</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="R43" s="2">
+        <v>0.186</v>
+      </c>
+      <c r="S43" s="2">
+        <v>0.223</v>
+      </c>
+      <c r="T43" s="3">
+        <f t="shared" si="2"/>
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B44" s="1">
+        <v>41</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44">
+        <v>128</v>
+      </c>
+      <c r="G44">
+        <v>200</v>
+      </c>
+      <c r="H44" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="9">
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="J44" s="2">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="K44" s="2">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="L44" s="3">
+        <f t="shared" si="0"/>
+        <v>0.34399999999999997</v>
+      </c>
+      <c r="M44" s="9">
+        <v>0.26300000000000001</v>
+      </c>
+      <c r="N44" s="2">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="O44" s="2">
+        <v>0.34699999999999998</v>
+      </c>
+      <c r="P44" s="3">
+        <f t="shared" si="1"/>
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="Q44" s="9">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="R44" s="2">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="S44" s="2">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="T44" s="3">
+        <f t="shared" si="2"/>
+        <v>0.20699999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B45" s="1">
+        <v>42</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45">
+        <v>256</v>
+      </c>
+      <c r="G45">
+        <v>200</v>
+      </c>
+      <c r="H45" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="9">
+        <v>0.376</v>
+      </c>
+      <c r="J45" s="2">
+        <v>0.372</v>
+      </c>
+      <c r="K45" s="2">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="L45" s="3">
+        <f t="shared" si="0"/>
+        <v>0.376</v>
+      </c>
+      <c r="M45" s="9">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="N45" s="2">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="O45" s="2">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="P45" s="3">
+        <f t="shared" si="1"/>
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="Q45" s="9">
+        <v>0.192</v>
+      </c>
+      <c r="R45" s="2">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="S45" s="2">
+        <v>0.221</v>
+      </c>
+      <c r="T45" s="3">
+        <f t="shared" si="2"/>
+        <v>0.22500000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B46" s="1">
+        <v>43</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46">
+        <v>512</v>
+      </c>
+      <c r="G46">
+        <v>200</v>
+      </c>
+      <c r="H46" t="s">
+        <v>13</v>
+      </c>
+      <c r="I46" s="9">
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="J46" s="2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="K46" s="2">
+        <v>0.29699999999999999</v>
+      </c>
+      <c r="L46" s="3">
+        <f t="shared" si="0"/>
+        <v>0.35799999999999998</v>
+      </c>
+      <c r="M46" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="N46" s="2">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="O46" s="2">
+        <v>0.34200000000000003</v>
+      </c>
+      <c r="P46" s="3">
+        <f t="shared" si="1"/>
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="Q46" s="9">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="R46" s="2">
+        <v>0.223</v>
+      </c>
+      <c r="S46" s="2">
+        <v>0.216</v>
+      </c>
+      <c r="T46" s="3">
+        <f t="shared" si="2"/>
+        <v>0.223</v>
       </c>
     </row>
   </sheetData>
@@ -5343,8 +6123,8 @@
     <mergeCell ref="M2:P2"/>
     <mergeCell ref="Q2:T2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I4:P40">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="J41:L46 I4:P40 N41:P46">
+    <cfRule type="colorScale" priority="247">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5355,8 +6135,44 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:T40">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="R41:T46 Q4:T40">
+    <cfRule type="colorScale" priority="254">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:L46">
+    <cfRule type="colorScale" priority="313">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4:P46">
+    <cfRule type="colorScale" priority="315">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q4:T46">
+    <cfRule type="colorScale" priority="317">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5373,7 +6189,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ECD2F34-0037-479F-8AE0-BBD704632229}">
-  <dimension ref="B2:T40"/>
+  <dimension ref="B2:T46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4.28515625" customWidth="1"/>
@@ -5492,7 +6308,7 @@
         <v>0.45300000000000001</v>
       </c>
       <c r="L4" s="3">
-        <f>MAX(I4:K4)</f>
+        <f t="shared" ref="L4:L46" si="0">MAX(I4:K4)</f>
         <v>0.59199999999999997</v>
       </c>
       <c r="M4" s="20">
@@ -5505,7 +6321,7 @@
         <v>0.45</v>
       </c>
       <c r="P4" s="3">
-        <f>MAX(M4:O4)</f>
+        <f t="shared" ref="P4:P46" si="1">MAX(M4:O4)</f>
         <v>0.53700000000000003</v>
       </c>
       <c r="Q4" s="20">
@@ -5518,7 +6334,7 @@
         <v>0.27500000000000002</v>
       </c>
       <c r="T4" s="3">
-        <f>MAX(Q4:S4)</f>
+        <f t="shared" ref="T4:T46" si="2">MAX(Q4:S4)</f>
         <v>0.30199999999999999</v>
       </c>
     </row>
@@ -5554,7 +6370,7 @@
         <v>0.47899999999999998</v>
       </c>
       <c r="L5" s="3">
-        <f>MAX(I5:K5)</f>
+        <f t="shared" si="0"/>
         <v>0.629</v>
       </c>
       <c r="M5" s="20">
@@ -5567,7 +6383,7 @@
         <v>0.46800000000000003</v>
       </c>
       <c r="P5" s="3">
-        <f>MAX(M5:O5)</f>
+        <f t="shared" si="1"/>
         <v>0.55500000000000005</v>
       </c>
       <c r="Q5" s="20">
@@ -5580,7 +6396,7 @@
         <v>0.3</v>
       </c>
       <c r="T5" s="3">
-        <f>MAX(Q5:S5)</f>
+        <f t="shared" si="2"/>
         <v>0.32600000000000001</v>
       </c>
     </row>
@@ -5616,7 +6432,7 @@
         <v>0.44500000000000001</v>
       </c>
       <c r="L6" s="3">
-        <f>MAX(I6:K6)</f>
+        <f t="shared" si="0"/>
         <v>0.61299999999999999</v>
       </c>
       <c r="M6" s="20">
@@ -5629,7 +6445,7 @@
         <v>0.46200000000000002</v>
       </c>
       <c r="P6" s="3">
-        <f>MAX(M6:O6)</f>
+        <f t="shared" si="1"/>
         <v>0.56200000000000006</v>
       </c>
       <c r="Q6" s="20">
@@ -5642,7 +6458,7 @@
         <v>0.29199999999999998</v>
       </c>
       <c r="T6" s="3">
-        <f>MAX(Q6:S6)</f>
+        <f t="shared" si="2"/>
         <v>0.32800000000000001</v>
       </c>
     </row>
@@ -5675,7 +6491,7 @@
         <v>0.435</v>
       </c>
       <c r="L7" s="3">
-        <f>MAX(I7:K7)</f>
+        <f t="shared" si="0"/>
         <v>0.61</v>
       </c>
       <c r="M7" s="20">
@@ -5688,7 +6504,7 @@
         <v>0.44400000000000001</v>
       </c>
       <c r="P7" s="3">
-        <f>MAX(M7:O7)</f>
+        <f t="shared" si="1"/>
         <v>0.53200000000000003</v>
       </c>
       <c r="Q7" s="20">
@@ -5701,7 +6517,7 @@
         <v>0.27300000000000002</v>
       </c>
       <c r="T7" s="3">
-        <f>MAX(Q7:S7)</f>
+        <f t="shared" si="2"/>
         <v>0.30299999999999999</v>
       </c>
     </row>
@@ -5734,7 +6550,7 @@
         <v>0.45400000000000001</v>
       </c>
       <c r="L8" s="3">
-        <f>MAX(I8:K8)</f>
+        <f t="shared" si="0"/>
         <v>0.62</v>
       </c>
       <c r="M8" s="20">
@@ -5747,7 +6563,7 @@
         <v>0.45700000000000002</v>
       </c>
       <c r="P8" s="3">
-        <f>MAX(M8:O8)</f>
+        <f t="shared" si="1"/>
         <v>0.54900000000000004</v>
       </c>
       <c r="Q8" s="20">
@@ -5760,7 +6576,7 @@
         <v>0.28399999999999997</v>
       </c>
       <c r="T8" s="3">
-        <f>MAX(Q8:S8)</f>
+        <f t="shared" si="2"/>
         <v>0.316</v>
       </c>
     </row>
@@ -5793,7 +6609,7 @@
         <v>0.438</v>
       </c>
       <c r="L9" s="3">
-        <f>MAX(I9:K9)</f>
+        <f t="shared" si="0"/>
         <v>0.59899999999999998</v>
       </c>
       <c r="M9" s="20">
@@ -5806,7 +6622,7 @@
         <v>0.44600000000000001</v>
       </c>
       <c r="P9" s="3">
-        <f>MAX(M9:O9)</f>
+        <f t="shared" si="1"/>
         <v>0.53600000000000003</v>
       </c>
       <c r="Q9" s="20">
@@ -5819,7 +6635,7 @@
         <v>0.27400000000000002</v>
       </c>
       <c r="T9" s="3">
-        <f>MAX(Q9:S9)</f>
+        <f t="shared" si="2"/>
         <v>0.30399999999999999</v>
       </c>
     </row>
@@ -5852,7 +6668,7 @@
         <v>0.45700000000000002</v>
       </c>
       <c r="L10" s="3">
-        <f>MAX(I10:K10)</f>
+        <f t="shared" si="0"/>
         <v>0.629</v>
       </c>
       <c r="M10" s="20">
@@ -5865,7 +6681,7 @@
         <v>0.46</v>
       </c>
       <c r="P10" s="3">
-        <f>MAX(M10:O10)</f>
+        <f t="shared" si="1"/>
         <v>0.56200000000000006</v>
       </c>
       <c r="Q10" s="20">
@@ -5878,7 +6694,7 @@
         <v>0.29499999999999998</v>
       </c>
       <c r="T10" s="3">
-        <f>MAX(Q10:S10)</f>
+        <f t="shared" si="2"/>
         <v>0.33100000000000002</v>
       </c>
     </row>
@@ -5911,7 +6727,7 @@
         <v>0.46200000000000002</v>
       </c>
       <c r="L11" s="3">
-        <f>MAX(I11:K11)</f>
+        <f t="shared" si="0"/>
         <v>0.626</v>
       </c>
       <c r="M11" s="20">
@@ -5924,7 +6740,7 @@
         <v>0.45400000000000001</v>
       </c>
       <c r="P11" s="3">
-        <f>MAX(M11:O11)</f>
+        <f t="shared" si="1"/>
         <v>0.55300000000000005</v>
       </c>
       <c r="Q11" s="20">
@@ -5937,7 +6753,7 @@
         <v>0.28499999999999998</v>
       </c>
       <c r="T11" s="3">
-        <f>MAX(Q11:S11)</f>
+        <f t="shared" si="2"/>
         <v>0.32300000000000001</v>
       </c>
     </row>
@@ -5970,7 +6786,7 @@
         <v>0.46500000000000002</v>
       </c>
       <c r="L12" s="3">
-        <f>MAX(I12:K12)</f>
+        <f t="shared" si="0"/>
         <v>0.60499999999999998</v>
       </c>
       <c r="M12" s="20">
@@ -5983,7 +6799,7 @@
         <v>0.44500000000000001</v>
       </c>
       <c r="P12" s="3">
-        <f>MAX(M12:O12)</f>
+        <f t="shared" si="1"/>
         <v>0.53400000000000003</v>
       </c>
       <c r="Q12" s="20">
@@ -5996,7 +6812,7 @@
         <v>0.27</v>
       </c>
       <c r="T12" s="3">
-        <f>MAX(Q12:S12)</f>
+        <f t="shared" si="2"/>
         <v>0.30599999999999999</v>
       </c>
     </row>
@@ -6029,7 +6845,7 @@
         <v>0.47299999999999998</v>
       </c>
       <c r="L13" s="3">
-        <f>MAX(I13:K13)</f>
+        <f t="shared" si="0"/>
         <v>0.65500000000000003</v>
       </c>
       <c r="M13" s="20">
@@ -6042,7 +6858,7 @@
         <v>0.47499999999999998</v>
       </c>
       <c r="P13" s="3">
-        <f>MAX(M13:O13)</f>
+        <f t="shared" si="1"/>
         <v>0.58899999999999997</v>
       </c>
       <c r="Q13" s="20">
@@ -6055,7 +6871,7 @@
         <v>0.308</v>
       </c>
       <c r="T13" s="3">
-        <f>MAX(Q13:S13)</f>
+        <f t="shared" si="2"/>
         <v>0.35499999999999998</v>
       </c>
     </row>
@@ -6088,7 +6904,7 @@
         <v>0.46100000000000002</v>
       </c>
       <c r="L14" s="3">
-        <f>MAX(I14:K14)</f>
+        <f t="shared" si="0"/>
         <v>0.624</v>
       </c>
       <c r="M14" s="20">
@@ -6101,7 +6917,7 @@
         <v>0.45400000000000001</v>
       </c>
       <c r="P14" s="3">
-        <f>MAX(M14:O14)</f>
+        <f t="shared" si="1"/>
         <v>0.55800000000000005</v>
       </c>
       <c r="Q14" s="20">
@@ -6114,7 +6930,7 @@
         <v>0.28599999999999998</v>
       </c>
       <c r="T14" s="3">
-        <f>MAX(Q14:S14)</f>
+        <f t="shared" si="2"/>
         <v>0.32700000000000001</v>
       </c>
     </row>
@@ -6147,7 +6963,7 @@
         <v>0.44600000000000001</v>
       </c>
       <c r="L15" s="3">
-        <f>MAX(I15:K15)</f>
+        <f t="shared" si="0"/>
         <v>0.60699999999999998</v>
       </c>
       <c r="M15" s="20">
@@ -6160,7 +6976,7 @@
         <v>0.441</v>
       </c>
       <c r="P15" s="3">
-        <f>MAX(M15:O15)</f>
+        <f t="shared" si="1"/>
         <v>0.54500000000000004</v>
       </c>
       <c r="Q15" s="20">
@@ -6173,7 +6989,7 @@
         <v>0.27300000000000002</v>
       </c>
       <c r="T15" s="3">
-        <f>MAX(Q15:S15)</f>
+        <f t="shared" si="2"/>
         <v>0.315</v>
       </c>
     </row>
@@ -6206,7 +7022,7 @@
         <v>0.44900000000000001</v>
       </c>
       <c r="L16" s="3">
-        <f>MAX(I16:K16)</f>
+        <f t="shared" si="0"/>
         <v>0.60499999999999998</v>
       </c>
       <c r="M16" s="20">
@@ -6219,7 +7035,7 @@
         <v>0.44400000000000001</v>
       </c>
       <c r="P16" s="3">
-        <f>MAX(M16:O16)</f>
+        <f t="shared" si="1"/>
         <v>0.54400000000000004</v>
       </c>
       <c r="Q16" s="20">
@@ -6232,7 +7048,7 @@
         <v>0.27300000000000002</v>
       </c>
       <c r="T16" s="3">
-        <f>MAX(Q16:S16)</f>
+        <f t="shared" si="2"/>
         <v>0.314</v>
       </c>
     </row>
@@ -6265,7 +7081,7 @@
         <v>0.495</v>
       </c>
       <c r="L17" s="3">
-        <f>MAX(I17:K17)</f>
+        <f t="shared" si="0"/>
         <v>0.63</v>
       </c>
       <c r="M17" s="20">
@@ -6278,7 +7094,7 @@
         <v>0.43099999999999999</v>
       </c>
       <c r="P17" s="3">
-        <f>MAX(M17:O17)</f>
+        <f t="shared" si="1"/>
         <v>0.55300000000000005</v>
       </c>
       <c r="Q17" s="20">
@@ -6291,7 +7107,7 @@
         <v>0.28100000000000003</v>
       </c>
       <c r="T17" s="3">
-        <f>MAX(Q17:S17)</f>
+        <f t="shared" si="2"/>
         <v>0.33</v>
       </c>
     </row>
@@ -6324,7 +7140,7 @@
         <v>0.42599999999999999</v>
       </c>
       <c r="L18" s="3">
-        <f>MAX(I18:K18)</f>
+        <f t="shared" si="0"/>
         <v>0.56100000000000005</v>
       </c>
       <c r="M18" s="20">
@@ -6337,7 +7153,7 @@
         <v>0.41</v>
       </c>
       <c r="P18" s="3">
-        <f>MAX(M18:O18)</f>
+        <f t="shared" si="1"/>
         <v>0.502</v>
       </c>
       <c r="Q18" s="20">
@@ -6350,7 +7166,7 @@
         <v>0.24099999999999999</v>
       </c>
       <c r="T18" s="3">
-        <f>MAX(Q18:S18)</f>
+        <f t="shared" si="2"/>
         <v>0.27400000000000002</v>
       </c>
     </row>
@@ -6386,7 +7202,7 @@
         <v>0.61399999999999999</v>
       </c>
       <c r="L19" s="3">
-        <f>MAX(I19:K19)</f>
+        <f t="shared" si="0"/>
         <v>0.75700000000000001</v>
       </c>
       <c r="M19" s="20">
@@ -6399,7 +7215,7 @@
         <v>0.64900000000000002</v>
       </c>
       <c r="P19" s="3">
-        <f>MAX(M19:O19)</f>
+        <f t="shared" si="1"/>
         <v>0.74</v>
       </c>
       <c r="Q19" s="20">
@@ -6412,7 +7228,7 @@
         <v>0.42799999999999999</v>
       </c>
       <c r="T19" s="3">
-        <f>MAX(Q19:S19)</f>
+        <f t="shared" si="2"/>
         <v>0.46</v>
       </c>
     </row>
@@ -6448,7 +7264,7 @@
         <v>0.63</v>
       </c>
       <c r="L20" s="3">
-        <f>MAX(I20:K20)</f>
+        <f t="shared" si="0"/>
         <v>0.75900000000000001</v>
       </c>
       <c r="M20" s="20">
@@ -6461,7 +7277,7 @@
         <v>0.66400000000000003</v>
       </c>
       <c r="P20" s="3">
-        <f>MAX(M20:O20)</f>
+        <f t="shared" si="1"/>
         <v>0.755</v>
       </c>
       <c r="Q20" s="20">
@@ -6474,7 +7290,7 @@
         <v>0.45500000000000002</v>
       </c>
       <c r="T20" s="3">
-        <f>MAX(Q20:S20)</f>
+        <f t="shared" si="2"/>
         <v>0.47899999999999998</v>
       </c>
     </row>
@@ -6510,7 +7326,7 @@
         <v>0.63</v>
       </c>
       <c r="L21" s="3">
-        <f>MAX(I21:K21)</f>
+        <f t="shared" si="0"/>
         <v>0.76900000000000002</v>
       </c>
       <c r="M21" s="20">
@@ -6523,7 +7339,7 @@
         <v>0.67</v>
       </c>
       <c r="P21" s="3">
-        <f>MAX(M21:O21)</f>
+        <f t="shared" si="1"/>
         <v>0.77700000000000002</v>
       </c>
       <c r="Q21" s="20">
@@ -6536,7 +7352,7 @@
         <v>0.48299999999999998</v>
       </c>
       <c r="T21" s="3">
-        <f>MAX(Q21:S21)</f>
+        <f t="shared" si="2"/>
         <v>0.52300000000000002</v>
       </c>
     </row>
@@ -6569,7 +7385,7 @@
         <v>0.41199999999999998</v>
       </c>
       <c r="L22" s="3">
-        <f>MAX(I22:K22)</f>
+        <f t="shared" si="0"/>
         <v>0.41199999999999998</v>
       </c>
       <c r="M22" s="20">
@@ -6582,7 +7398,7 @@
         <v>0.53200000000000003</v>
       </c>
       <c r="P22" s="3">
-        <f>MAX(M22:O22)</f>
+        <f t="shared" si="1"/>
         <v>0.53200000000000003</v>
       </c>
       <c r="Q22" s="20">
@@ -6595,7 +7411,7 @@
         <v>0.27100000000000002</v>
       </c>
       <c r="T22" s="3">
-        <f>MAX(Q22:S22)</f>
+        <f t="shared" si="2"/>
         <v>0.27100000000000002</v>
       </c>
     </row>
@@ -6628,7 +7444,7 @@
         <v>0.48599999999999999</v>
       </c>
       <c r="L23" s="3">
-        <f>MAX(I23:K23)</f>
+        <f t="shared" si="0"/>
         <v>0.48599999999999999</v>
       </c>
       <c r="M23" s="20">
@@ -6641,7 +7457,7 @@
         <v>0.56599999999999995</v>
       </c>
       <c r="P23" s="3">
-        <f>MAX(M23:O23)</f>
+        <f t="shared" si="1"/>
         <v>0.56599999999999995</v>
       </c>
       <c r="Q23" s="20">
@@ -6654,7 +7470,7 @@
         <v>0.30399999999999999</v>
       </c>
       <c r="T23" s="3">
-        <f>MAX(Q23:S23)</f>
+        <f t="shared" si="2"/>
         <v>0.30399999999999999</v>
       </c>
     </row>
@@ -6687,7 +7503,7 @@
         <v>0.48799999999999999</v>
       </c>
       <c r="L24" s="3">
-        <f>MAX(I24:K24)</f>
+        <f t="shared" si="0"/>
         <v>0.48799999999999999</v>
       </c>
       <c r="M24" s="20">
@@ -6700,7 +7516,7 @@
         <v>0.56399999999999995</v>
       </c>
       <c r="P24" s="3">
-        <f>MAX(M24:O24)</f>
+        <f t="shared" si="1"/>
         <v>0.56399999999999995</v>
       </c>
       <c r="Q24" s="20">
@@ -6713,7 +7529,7 @@
         <v>0.30399999999999999</v>
       </c>
       <c r="T24" s="3">
-        <f>MAX(Q24:S24)</f>
+        <f t="shared" si="2"/>
         <v>0.30399999999999999</v>
       </c>
     </row>
@@ -6746,7 +7562,7 @@
         <v>0.435</v>
       </c>
       <c r="L25" s="3">
-        <f>MAX(I25:K25)</f>
+        <f t="shared" si="0"/>
         <v>0.435</v>
       </c>
       <c r="M25" s="20">
@@ -6759,7 +7575,7 @@
         <v>0.54900000000000004</v>
       </c>
       <c r="P25" s="3">
-        <f>MAX(M25:O25)</f>
+        <f t="shared" si="1"/>
         <v>0.54900000000000004</v>
       </c>
       <c r="Q25" s="20">
@@ -6772,7 +7588,7 @@
         <v>0.30099999999999999</v>
       </c>
       <c r="T25" s="3">
-        <f>MAX(Q25:S25)</f>
+        <f t="shared" si="2"/>
         <v>0.30099999999999999</v>
       </c>
     </row>
@@ -6805,7 +7621,7 @@
         <v>0.41499999999999998</v>
       </c>
       <c r="L26" s="3">
-        <f>MAX(I26:K26)</f>
+        <f t="shared" si="0"/>
         <v>0.41499999999999998</v>
       </c>
       <c r="M26" s="20">
@@ -6818,7 +7634,7 @@
         <v>0.51500000000000001</v>
       </c>
       <c r="P26" s="3">
-        <f>MAX(M26:O26)</f>
+        <f t="shared" si="1"/>
         <v>0.51500000000000001</v>
       </c>
       <c r="Q26" s="20">
@@ -6831,7 +7647,7 @@
         <v>0.27800000000000002</v>
       </c>
       <c r="T26" s="3">
-        <f>MAX(Q26:S26)</f>
+        <f t="shared" si="2"/>
         <v>0.27800000000000002</v>
       </c>
     </row>
@@ -6867,7 +7683,7 @@
         <v>0.46200000000000002</v>
       </c>
       <c r="L27" s="3">
-        <f>MAX(I27:K27)</f>
+        <f t="shared" si="0"/>
         <v>0.48899999999999999</v>
       </c>
       <c r="M27" s="20">
@@ -6880,7 +7696,7 @@
         <v>0.51900000000000002</v>
       </c>
       <c r="P27" s="3">
-        <f>MAX(M27:O27)</f>
+        <f t="shared" si="1"/>
         <v>0.52600000000000002</v>
       </c>
       <c r="Q27" s="20">
@@ -6893,7 +7709,7 @@
         <v>0.27800000000000002</v>
       </c>
       <c r="T27" s="3">
-        <f>MAX(Q27:S27)</f>
+        <f t="shared" si="2"/>
         <v>0.27800000000000002</v>
       </c>
     </row>
@@ -6929,7 +7745,7 @@
         <v>0.49099999999999999</v>
       </c>
       <c r="L28" s="3">
-        <f>MAX(I28:K28)</f>
+        <f t="shared" si="0"/>
         <v>0.51</v>
       </c>
       <c r="M28" s="20">
@@ -6942,7 +7758,7 @@
         <v>0.52400000000000002</v>
       </c>
       <c r="P28" s="3">
-        <f>MAX(M28:O28)</f>
+        <f t="shared" si="1"/>
         <v>0.54</v>
       </c>
       <c r="Q28" s="20">
@@ -6955,7 +7771,7 @@
         <v>0.28799999999999998</v>
       </c>
       <c r="T28" s="3">
-        <f>MAX(Q28:S28)</f>
+        <f t="shared" si="2"/>
         <v>0.28799999999999998</v>
       </c>
     </row>
@@ -6991,7 +7807,7 @@
         <v>0.44400000000000001</v>
       </c>
       <c r="L29" s="3">
-        <f>MAX(I29:K29)</f>
+        <f t="shared" si="0"/>
         <v>0.45500000000000002</v>
       </c>
       <c r="M29" s="20">
@@ -7004,7 +7820,7 @@
         <v>0.49199999999999999</v>
       </c>
       <c r="P29" s="3">
-        <f>MAX(M29:O29)</f>
+        <f t="shared" si="1"/>
         <v>0.504</v>
       </c>
       <c r="Q29" s="20">
@@ -7017,7 +7833,7 @@
         <v>0.27300000000000002</v>
       </c>
       <c r="T29" s="3">
-        <f>MAX(Q29:S29)</f>
+        <f t="shared" si="2"/>
         <v>0.27400000000000002</v>
       </c>
     </row>
@@ -7053,7 +7869,7 @@
         <v>0.435</v>
       </c>
       <c r="L30" s="3">
-        <f>MAX(I30:K30)</f>
+        <f t="shared" si="0"/>
         <v>0.51700000000000002</v>
       </c>
       <c r="M30" s="20">
@@ -7066,7 +7882,7 @@
         <v>0.46100000000000002</v>
       </c>
       <c r="P30" s="3">
-        <f>MAX(M30:O30)</f>
+        <f t="shared" si="1"/>
         <v>0.51100000000000001</v>
       </c>
       <c r="Q30" s="20">
@@ -7079,7 +7895,7 @@
         <v>0.26600000000000001</v>
       </c>
       <c r="T30" s="3">
-        <f>MAX(Q30:S30)</f>
+        <f t="shared" si="2"/>
         <v>0.27</v>
       </c>
     </row>
@@ -7115,7 +7931,7 @@
         <v>0.46600000000000003</v>
       </c>
       <c r="L31" s="3">
-        <f>MAX(I31:K31)</f>
+        <f t="shared" si="0"/>
         <v>0.53300000000000003</v>
       </c>
       <c r="M31" s="20">
@@ -7128,7 +7944,7 @@
         <v>0.46400000000000002</v>
       </c>
       <c r="P31" s="3">
-        <f>MAX(M31:O31)</f>
+        <f t="shared" si="1"/>
         <v>0.52400000000000002</v>
       </c>
       <c r="Q31" s="20">
@@ -7141,7 +7957,7 @@
         <v>0.27600000000000002</v>
       </c>
       <c r="T31" s="3">
-        <f>MAX(Q31:S31)</f>
+        <f t="shared" si="2"/>
         <v>0.29099999999999998</v>
       </c>
     </row>
@@ -7177,7 +7993,7 @@
         <v>0.432</v>
       </c>
       <c r="L32" s="3">
-        <f>MAX(I32:K32)</f>
+        <f t="shared" si="0"/>
         <v>0.48699999999999999</v>
       </c>
       <c r="M32" s="20">
@@ -7190,7 +8006,7 @@
         <v>0.433</v>
       </c>
       <c r="P32" s="3">
-        <f>MAX(M32:O32)</f>
+        <f t="shared" si="1"/>
         <v>0.49199999999999999</v>
       </c>
       <c r="Q32" s="20">
@@ -7203,7 +8019,7 @@
         <v>0.25900000000000001</v>
       </c>
       <c r="T32" s="3">
-        <f>MAX(Q32:S32)</f>
+        <f t="shared" si="2"/>
         <v>0.27600000000000002</v>
       </c>
     </row>
@@ -7239,7 +8055,7 @@
         <v>0.36099999999999999</v>
       </c>
       <c r="L33" s="3">
-        <f>MAX(I33:K33)</f>
+        <f t="shared" si="0"/>
         <v>0.36099999999999999</v>
       </c>
       <c r="M33" s="20">
@@ -7252,7 +8068,7 @@
         <v>0.42799999999999999</v>
       </c>
       <c r="P33" s="3">
-        <f>MAX(M33:O33)</f>
+        <f t="shared" si="1"/>
         <v>0.42799999999999999</v>
       </c>
       <c r="Q33" s="20">
@@ -7265,7 +8081,7 @@
         <v>0.20599999999999999</v>
       </c>
       <c r="T33" s="3">
-        <f>MAX(Q33:S33)</f>
+        <f t="shared" si="2"/>
         <v>0.20599999999999999</v>
       </c>
     </row>
@@ -7301,7 +8117,7 @@
         <v>0.46</v>
       </c>
       <c r="L34" s="3">
-        <f>MAX(I34:K34)</f>
+        <f t="shared" si="0"/>
         <v>0.46</v>
       </c>
       <c r="M34" s="20">
@@ -7314,7 +8130,7 @@
         <v>0.51100000000000001</v>
       </c>
       <c r="P34" s="3">
-        <f>MAX(M34:O34)</f>
+        <f t="shared" si="1"/>
         <v>0.51100000000000001</v>
       </c>
       <c r="Q34" s="20">
@@ -7327,7 +8143,7 @@
         <v>0.27</v>
       </c>
       <c r="T34" s="3">
-        <f>MAX(Q34:S34)</f>
+        <f t="shared" si="2"/>
         <v>0.27</v>
       </c>
     </row>
@@ -7363,7 +8179,7 @@
         <v>0.41299999999999998</v>
       </c>
       <c r="L35" s="3">
-        <f>MAX(I35:K35)</f>
+        <f t="shared" si="0"/>
         <v>0.41299999999999998</v>
       </c>
       <c r="M35" s="20">
@@ -7376,7 +8192,7 @@
         <v>0.51</v>
       </c>
       <c r="P35" s="3">
-        <f>MAX(M35:O35)</f>
+        <f t="shared" si="1"/>
         <v>0.51</v>
       </c>
       <c r="Q35" s="20">
@@ -7389,7 +8205,7 @@
         <v>0.27300000000000002</v>
       </c>
       <c r="T35" s="3">
-        <f>MAX(Q35:S35)</f>
+        <f t="shared" si="2"/>
         <v>0.27300000000000002</v>
       </c>
     </row>
@@ -7422,7 +8238,7 @@
         <v>0.42799999999999999</v>
       </c>
       <c r="L36" s="3">
-        <f>MAX(I36:K36)</f>
+        <f t="shared" si="0"/>
         <v>0.43</v>
       </c>
       <c r="M36" s="20">
@@ -7435,7 +8251,7 @@
         <v>0.51300000000000001</v>
       </c>
       <c r="P36" s="3">
-        <f>MAX(M36:O36)</f>
+        <f t="shared" si="1"/>
         <v>0.51300000000000001</v>
       </c>
       <c r="Q36" s="20">
@@ -7448,7 +8264,7 @@
         <v>0.25900000000000001</v>
       </c>
       <c r="T36" s="3">
-        <f>MAX(Q36:S36)</f>
+        <f t="shared" si="2"/>
         <v>0.25900000000000001</v>
       </c>
     </row>
@@ -7481,7 +8297,7 @@
         <v>0.48899999999999999</v>
       </c>
       <c r="L37" s="3">
-        <f>MAX(I37:K37)</f>
+        <f t="shared" si="0"/>
         <v>0.496</v>
       </c>
       <c r="M37" s="20">
@@ -7494,7 +8310,7 @@
         <v>0.55200000000000005</v>
       </c>
       <c r="P37" s="3">
-        <f>MAX(M37:O37)</f>
+        <f t="shared" si="1"/>
         <v>0.55200000000000005</v>
       </c>
       <c r="Q37" s="20">
@@ -7507,7 +8323,7 @@
         <v>0.29799999999999999</v>
       </c>
       <c r="T37" s="3">
-        <f>MAX(Q37:S37)</f>
+        <f t="shared" si="2"/>
         <v>0.29799999999999999</v>
       </c>
     </row>
@@ -7540,7 +8356,7 @@
         <v>0.48899999999999999</v>
       </c>
       <c r="L38" s="3">
-        <f>MAX(I38:K38)</f>
+        <f t="shared" si="0"/>
         <v>0.49399999999999999</v>
       </c>
       <c r="M38" s="20">
@@ -7553,7 +8369,7 @@
         <v>0.55300000000000005</v>
       </c>
       <c r="P38" s="3">
-        <f>MAX(M38:O38)</f>
+        <f t="shared" si="1"/>
         <v>0.55300000000000005</v>
       </c>
       <c r="Q38" s="20">
@@ -7566,7 +8382,7 @@
         <v>0.29899999999999999</v>
       </c>
       <c r="T38" s="3">
-        <f>MAX(Q38:S38)</f>
+        <f t="shared" si="2"/>
         <v>0.29899999999999999</v>
       </c>
     </row>
@@ -7599,7 +8415,7 @@
         <v>0.46800000000000003</v>
       </c>
       <c r="L39" s="3">
-        <f>MAX(I39:K39)</f>
+        <f t="shared" si="0"/>
         <v>0.502</v>
       </c>
       <c r="M39" s="20">
@@ -7612,7 +8428,7 @@
         <v>0.54100000000000004</v>
       </c>
       <c r="P39" s="3">
-        <f>MAX(M39:O39)</f>
+        <f t="shared" si="1"/>
         <v>0.54100000000000004</v>
       </c>
       <c r="Q39" s="20">
@@ -7625,7 +8441,7 @@
         <v>0.30099999999999999</v>
       </c>
       <c r="T39" s="3">
-        <f>MAX(Q39:S39)</f>
+        <f t="shared" si="2"/>
         <v>0.30099999999999999</v>
       </c>
     </row>
@@ -7658,7 +8474,7 @@
         <v>0.43099999999999999</v>
       </c>
       <c r="L40" s="3">
-        <f>MAX(I40:K40)</f>
+        <f t="shared" si="0"/>
         <v>0.45700000000000002</v>
       </c>
       <c r="M40" s="20">
@@ -7671,7 +8487,7 @@
         <v>0.495</v>
       </c>
       <c r="P40" s="3">
-        <f>MAX(M40:O40)</f>
+        <f t="shared" si="1"/>
         <v>0.495</v>
       </c>
       <c r="Q40" s="20">
@@ -7684,8 +8500,380 @@
         <v>0.26900000000000002</v>
       </c>
       <c r="T40" s="3">
-        <f>MAX(Q40:S40)</f>
+        <f t="shared" si="2"/>
         <v>0.26900000000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B41" s="1">
+        <v>38</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41">
+        <v>128</v>
+      </c>
+      <c r="G41">
+        <v>200</v>
+      </c>
+      <c r="H41" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="9">
+        <v>0.49399999999999999</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0.496</v>
+      </c>
+      <c r="K41" s="2">
+        <v>0.46899999999999997</v>
+      </c>
+      <c r="L41" s="3">
+        <f t="shared" si="0"/>
+        <v>0.496</v>
+      </c>
+      <c r="M41" s="9">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="N41" s="2">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="O41" s="2">
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="P41" s="3">
+        <f t="shared" si="1"/>
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="Q41" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="R41" s="2">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="S41" s="2">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="T41" s="3">
+        <f t="shared" si="2"/>
+        <v>0.28100000000000003</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B42" s="1">
+        <v>39</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42">
+        <v>256</v>
+      </c>
+      <c r="G42">
+        <v>200</v>
+      </c>
+      <c r="H42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="9">
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="J42" s="2">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="K42" s="2">
+        <v>0.499</v>
+      </c>
+      <c r="L42" s="3">
+        <f t="shared" si="0"/>
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="M42" s="9">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="N42" s="2">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="O42" s="2">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="P42" s="3">
+        <f t="shared" si="1"/>
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="Q42" s="9">
+        <v>0.248</v>
+      </c>
+      <c r="R42" s="2">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="S42" s="2">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="T42" s="3">
+        <f t="shared" si="2"/>
+        <v>0.29899999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B43" s="1">
+        <v>40</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43">
+        <v>512</v>
+      </c>
+      <c r="G43">
+        <v>200</v>
+      </c>
+      <c r="H43" t="s">
+        <v>13</v>
+      </c>
+      <c r="I43" s="9">
+        <v>0.496</v>
+      </c>
+      <c r="J43" s="2">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="K43" s="2">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="L43" s="3">
+        <f t="shared" si="0"/>
+        <v>0.496</v>
+      </c>
+      <c r="M43" s="9">
+        <v>0.434</v>
+      </c>
+      <c r="N43" s="2">
+        <v>0.52</v>
+      </c>
+      <c r="O43" s="2">
+        <v>0.504</v>
+      </c>
+      <c r="P43" s="3">
+        <f t="shared" si="1"/>
+        <v>0.52</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="R43" s="2">
+        <v>0.28299999999999997</v>
+      </c>
+      <c r="S43" s="2">
+        <v>0.29299999999999998</v>
+      </c>
+      <c r="T43" s="3">
+        <f t="shared" si="2"/>
+        <v>0.29299999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B44" s="1">
+        <v>41</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44">
+        <v>128</v>
+      </c>
+      <c r="G44">
+        <v>200</v>
+      </c>
+      <c r="H44" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="9">
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="J44" s="2">
+        <v>0.50800000000000001</v>
+      </c>
+      <c r="K44" s="2">
+        <v>0.434</v>
+      </c>
+      <c r="L44" s="3">
+        <f t="shared" si="0"/>
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="M44" s="9">
+        <v>0.45</v>
+      </c>
+      <c r="N44" s="2">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="O44" s="2">
+        <v>0.46700000000000003</v>
+      </c>
+      <c r="P44" s="3">
+        <f t="shared" si="1"/>
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="Q44" s="9">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="R44" s="2">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="S44" s="2">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="T44" s="3">
+        <f t="shared" si="2"/>
+        <v>0.27800000000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B45" s="1">
+        <v>42</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45">
+        <v>256</v>
+      </c>
+      <c r="G45">
+        <v>200</v>
+      </c>
+      <c r="H45" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="9">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="J45" s="2">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="K45" s="2">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="L45" s="3">
+        <f t="shared" si="0"/>
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="M45" s="9">
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="N45" s="2">
+        <v>0.53100000000000003</v>
+      </c>
+      <c r="O45" s="2">
+        <v>0.46400000000000002</v>
+      </c>
+      <c r="P45" s="3">
+        <f t="shared" si="1"/>
+        <v>0.53100000000000003</v>
+      </c>
+      <c r="Q45" s="9">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="R45" s="2">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="S45" s="2">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="T45" s="3">
+        <f t="shared" si="2"/>
+        <v>0.29499999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B46" s="1">
+        <v>43</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46">
+        <v>512</v>
+      </c>
+      <c r="G46">
+        <v>200</v>
+      </c>
+      <c r="H46" t="s">
+        <v>13</v>
+      </c>
+      <c r="I46" s="9">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="J46" s="2">
+        <v>0.51600000000000001</v>
+      </c>
+      <c r="K46" s="2">
+        <v>0.439</v>
+      </c>
+      <c r="L46" s="3">
+        <f t="shared" si="0"/>
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="M46" s="9">
+        <v>0.48099999999999998</v>
+      </c>
+      <c r="N46" s="2">
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="O46" s="2">
+        <v>0.45600000000000002</v>
+      </c>
+      <c r="P46" s="3">
+        <f t="shared" si="1"/>
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="Q46" s="9">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="R46" s="2">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="S46" s="2">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="T46" s="3">
+        <f t="shared" si="2"/>
+        <v>0.30599999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -7699,8 +8887,8 @@
     <mergeCell ref="M2:P2"/>
     <mergeCell ref="Q2:T2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I4:P40">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="J41:L46 I4:P40 N41:P46">
+    <cfRule type="colorScale" priority="107">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7711,8 +8899,44 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:T40">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="R41:T46 Q4:T40">
+    <cfRule type="colorScale" priority="112">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:L46">
+    <cfRule type="colorScale" priority="115">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4:P46">
+    <cfRule type="colorScale" priority="117">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q4:T46">
+    <cfRule type="colorScale" priority="119">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7729,7 +8953,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE3605DF-CC1B-4120-B106-3EBE857924BB}">
-  <dimension ref="B2:P40"/>
+  <dimension ref="B2:T46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4.28515625" customWidth="1"/>
@@ -7830,7 +9054,7 @@
         <v>0.625</v>
       </c>
       <c r="L4" s="22">
-        <f>MAX(I4:K4)</f>
+        <f t="shared" ref="L4:L46" si="0">MAX(I4:K4)</f>
         <v>0.70799999999999996</v>
       </c>
       <c r="M4" s="20">
@@ -7843,7 +9067,7 @@
         <v>0.29099999999999998</v>
       </c>
       <c r="P4" s="3">
-        <f>MAX(M4:O4)</f>
+        <f t="shared" ref="P4:P46" si="1">MAX(M4:O4)</f>
         <v>0.29099999999999998</v>
       </c>
     </row>
@@ -7879,7 +9103,7 @@
         <v>0.63</v>
       </c>
       <c r="L5" s="22">
-        <f>MAX(I5:K5)</f>
+        <f t="shared" si="0"/>
         <v>0.72199999999999998</v>
       </c>
       <c r="M5" s="20">
@@ -7892,7 +9116,7 @@
         <v>0.30399999999999999</v>
       </c>
       <c r="P5" s="3">
-        <f>MAX(M5:O5)</f>
+        <f t="shared" si="1"/>
         <v>0.30399999999999999</v>
       </c>
     </row>
@@ -7928,7 +9152,7 @@
         <v>0.63400000000000001</v>
       </c>
       <c r="L6" s="22">
-        <f>MAX(I6:K6)</f>
+        <f t="shared" si="0"/>
         <v>0.73699999999999999</v>
       </c>
       <c r="M6" s="20">
@@ -7941,7 +9165,7 @@
         <v>0.30099999999999999</v>
       </c>
       <c r="P6" s="3">
-        <f>MAX(M6:O6)</f>
+        <f t="shared" si="1"/>
         <v>0.309</v>
       </c>
     </row>
@@ -7974,7 +9198,7 @@
         <v>0.61799999999999999</v>
       </c>
       <c r="L7" s="22">
-        <f>MAX(I7:K7)</f>
+        <f t="shared" si="0"/>
         <v>0.69899999999999995</v>
       </c>
       <c r="M7" s="20">
@@ -7987,7 +9211,7 @@
         <v>0.28699999999999998</v>
       </c>
       <c r="P7" s="3">
-        <f>MAX(M7:O7)</f>
+        <f t="shared" si="1"/>
         <v>0.28699999999999998</v>
       </c>
     </row>
@@ -8020,7 +9244,7 @@
         <v>0.621</v>
       </c>
       <c r="L8" s="22">
-        <f>MAX(I8:K8)</f>
+        <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
       <c r="M8" s="20">
@@ -8033,7 +9257,7 @@
         <v>0.28599999999999998</v>
       </c>
       <c r="P8" s="3">
-        <f>MAX(M8:O8)</f>
+        <f t="shared" si="1"/>
         <v>0.28599999999999998</v>
       </c>
     </row>
@@ -8066,7 +9290,7 @@
         <v>0.60799999999999998</v>
       </c>
       <c r="L9" s="22">
-        <f>MAX(I9:K9)</f>
+        <f t="shared" si="0"/>
         <v>0.68400000000000005</v>
       </c>
       <c r="M9" s="20">
@@ -8079,7 +9303,7 @@
         <v>0.26700000000000002</v>
       </c>
       <c r="P9" s="3">
-        <f>MAX(M9:O9)</f>
+        <f t="shared" si="1"/>
         <v>0.26700000000000002</v>
       </c>
     </row>
@@ -8112,7 +9336,7 @@
         <v>0.629</v>
       </c>
       <c r="L10" s="22">
-        <f>MAX(I10:K10)</f>
+        <f t="shared" si="0"/>
         <v>0.72499999999999998</v>
       </c>
       <c r="M10" s="20">
@@ -8125,7 +9349,7 @@
         <v>0.3</v>
       </c>
       <c r="P10" s="3">
-        <f>MAX(M10:O10)</f>
+        <f t="shared" si="1"/>
         <v>0.30399999999999999</v>
       </c>
     </row>
@@ -8158,7 +9382,7 @@
         <v>0.61</v>
       </c>
       <c r="L11" s="22">
-        <f>MAX(I11:K11)</f>
+        <f t="shared" si="0"/>
         <v>0.70899999999999996</v>
       </c>
       <c r="M11" s="20">
@@ -8171,7 +9395,7 @@
         <v>0.27200000000000002</v>
       </c>
       <c r="P11" s="3">
-        <f>MAX(M11:O11)</f>
+        <f t="shared" si="1"/>
         <v>0.28000000000000003</v>
       </c>
     </row>
@@ -8204,7 +9428,7 @@
         <v>0.60799999999999998</v>
       </c>
       <c r="L12" s="22">
-        <f>MAX(I12:K12)</f>
+        <f t="shared" si="0"/>
         <v>0.69899999999999995</v>
       </c>
       <c r="M12" s="20">
@@ -8217,7 +9441,7 @@
         <v>0.27800000000000002</v>
       </c>
       <c r="P12" s="3">
-        <f>MAX(M12:O12)</f>
+        <f t="shared" si="1"/>
         <v>0.28399999999999997</v>
       </c>
     </row>
@@ -8250,7 +9474,7 @@
         <v>0.63</v>
       </c>
       <c r="L13" s="22">
-        <f>MAX(I13:K13)</f>
+        <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
       <c r="M13" s="20">
@@ -8263,7 +9487,7 @@
         <v>0.312</v>
       </c>
       <c r="P13" s="3">
-        <f>MAX(M13:O13)</f>
+        <f t="shared" si="1"/>
         <v>0.32500000000000001</v>
       </c>
     </row>
@@ -8296,7 +9520,7 @@
         <v>0.60299999999999998</v>
       </c>
       <c r="L14" s="22">
-        <f>MAX(I14:K14)</f>
+        <f t="shared" si="0"/>
         <v>0.71699999999999997</v>
       </c>
       <c r="M14" s="20">
@@ -8309,7 +9533,7 @@
         <v>0.26900000000000002</v>
       </c>
       <c r="P14" s="3">
-        <f>MAX(M14:O14)</f>
+        <f t="shared" si="1"/>
         <v>0.27700000000000002</v>
       </c>
     </row>
@@ -8342,7 +9566,7 @@
         <v>0.59399999999999997</v>
       </c>
       <c r="L15" s="22">
-        <f>MAX(I15:K15)</f>
+        <f t="shared" si="0"/>
         <v>0.70699999999999996</v>
       </c>
       <c r="M15" s="20">
@@ -8355,7 +9579,7 @@
         <v>0.25900000000000001</v>
       </c>
       <c r="P15" s="3">
-        <f>MAX(M15:O15)</f>
+        <f t="shared" si="1"/>
         <v>0.25900000000000001</v>
       </c>
     </row>
@@ -8388,7 +9612,7 @@
         <v>0.60099999999999998</v>
       </c>
       <c r="L16" s="22">
-        <f>MAX(I16:K16)</f>
+        <f t="shared" si="0"/>
         <v>0.71399999999999997</v>
       </c>
       <c r="M16" s="20">
@@ -8401,7 +9625,7 @@
         <v>0.26400000000000001</v>
       </c>
       <c r="P16" s="3">
-        <f>MAX(M16:O16)</f>
+        <f t="shared" si="1"/>
         <v>0.27800000000000002</v>
       </c>
     </row>
@@ -8434,7 +9658,7 @@
         <v>0.57699999999999996</v>
       </c>
       <c r="L17" s="22">
-        <f>MAX(I17:K17)</f>
+        <f t="shared" si="0"/>
         <v>0.71599999999999997</v>
       </c>
       <c r="M17" s="20">
@@ -8447,7 +9671,7 @@
         <v>0.27400000000000002</v>
       </c>
       <c r="P17" s="3">
-        <f>MAX(M17:O17)</f>
+        <f t="shared" si="1"/>
         <v>0.30199999999999999</v>
       </c>
     </row>
@@ -8480,7 +9704,7 @@
         <v>0.56599999999999995</v>
       </c>
       <c r="L18" s="22">
-        <f>MAX(I18:K18)</f>
+        <f t="shared" si="0"/>
         <v>0.67</v>
       </c>
       <c r="M18" s="20">
@@ -8493,7 +9717,7 @@
         <v>0.23</v>
       </c>
       <c r="P18" s="3">
-        <f>MAX(M18:O18)</f>
+        <f t="shared" si="1"/>
         <v>0.23400000000000001</v>
       </c>
     </row>
@@ -8529,7 +9753,7 @@
         <v>0.66700000000000004</v>
       </c>
       <c r="L19" s="22">
-        <f>MAX(I19:K19)</f>
+        <f t="shared" si="0"/>
         <v>0.71099999999999997</v>
       </c>
       <c r="M19" s="20">
@@ -8542,7 +9766,7 @@
         <v>0.307</v>
       </c>
       <c r="P19" s="3">
-        <f>MAX(M19:O19)</f>
+        <f t="shared" si="1"/>
         <v>0.307</v>
       </c>
     </row>
@@ -8578,7 +9802,7 @@
         <v>0.68200000000000005</v>
       </c>
       <c r="L20" s="22">
-        <f>MAX(I20:K20)</f>
+        <f t="shared" si="0"/>
         <v>0.74</v>
       </c>
       <c r="M20" s="20">
@@ -8591,7 +9815,7 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="P20" s="3">
-        <f>MAX(M20:O20)</f>
+        <f t="shared" si="1"/>
         <v>0.33300000000000002</v>
       </c>
     </row>
@@ -8627,7 +9851,7 @@
         <v>0.69499999999999995</v>
       </c>
       <c r="L21" s="22">
-        <f>MAX(I21:K21)</f>
+        <f t="shared" si="0"/>
         <v>0.77400000000000002</v>
       </c>
       <c r="M21" s="20">
@@ -8640,7 +9864,7 @@
         <v>0.38600000000000001</v>
       </c>
       <c r="P21" s="3">
-        <f>MAX(M21:O21)</f>
+        <f t="shared" si="1"/>
         <v>0.38600000000000001</v>
       </c>
     </row>
@@ -8673,7 +9897,7 @@
         <v>0.70799999999999996</v>
       </c>
       <c r="L22" s="22">
-        <f>MAX(I22:K22)</f>
+        <f t="shared" si="0"/>
         <v>0.70799999999999996</v>
       </c>
       <c r="M22" s="20">
@@ -8686,7 +9910,7 @@
         <v>0.25700000000000001</v>
       </c>
       <c r="P22" s="3">
-        <f>MAX(M22:O22)</f>
+        <f t="shared" si="1"/>
         <v>0.25700000000000001</v>
       </c>
     </row>
@@ -8719,7 +9943,7 @@
         <v>0.748</v>
       </c>
       <c r="L23" s="22">
-        <f>MAX(I23:K23)</f>
+        <f t="shared" si="0"/>
         <v>0.748</v>
       </c>
       <c r="M23" s="20">
@@ -8732,7 +9956,7 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="P23" s="3">
-        <f>MAX(M23:O23)</f>
+        <f t="shared" si="1"/>
         <v>0.29699999999999999</v>
       </c>
     </row>
@@ -8765,7 +9989,7 @@
         <v>0.745</v>
       </c>
       <c r="L24" s="22">
-        <f>MAX(I24:K24)</f>
+        <f t="shared" si="0"/>
         <v>0.745</v>
       </c>
       <c r="M24" s="20">
@@ -8778,7 +10002,7 @@
         <v>0.29799999999999999</v>
       </c>
       <c r="P24" s="3">
-        <f>MAX(M24:O24)</f>
+        <f t="shared" si="1"/>
         <v>0.29799999999999999</v>
       </c>
     </row>
@@ -8811,7 +10035,7 @@
         <v>0.71499999999999997</v>
       </c>
       <c r="L25" s="22">
-        <f>MAX(I25:K25)</f>
+        <f t="shared" si="0"/>
         <v>0.71499999999999997</v>
       </c>
       <c r="M25" s="20">
@@ -8824,7 +10048,7 @@
         <v>0.29499999999999998</v>
       </c>
       <c r="P25" s="3">
-        <f>MAX(M25:O25)</f>
+        <f t="shared" si="1"/>
         <v>0.29499999999999998</v>
       </c>
     </row>
@@ -8857,7 +10081,7 @@
         <v>0.69299999999999995</v>
       </c>
       <c r="L26" s="22">
-        <f>MAX(I26:K26)</f>
+        <f t="shared" si="0"/>
         <v>0.69299999999999995</v>
       </c>
       <c r="M26" s="20">
@@ -8870,7 +10094,7 @@
         <v>0.27400000000000002</v>
       </c>
       <c r="P26" s="3">
-        <f>MAX(M26:O26)</f>
+        <f t="shared" si="1"/>
         <v>0.27400000000000002</v>
       </c>
     </row>
@@ -8906,7 +10130,7 @@
         <v>0.70199999999999996</v>
       </c>
       <c r="L27" s="22">
-        <f>MAX(I27:K27)</f>
+        <f t="shared" si="0"/>
         <v>0.70699999999999996</v>
       </c>
       <c r="M27" s="20">
@@ -8919,7 +10143,7 @@
         <v>0.27600000000000002</v>
       </c>
       <c r="P27" s="3">
-        <f>MAX(M27:O27)</f>
+        <f t="shared" si="1"/>
         <v>0.27600000000000002</v>
       </c>
     </row>
@@ -8955,7 +10179,7 @@
         <v>0.70499999999999996</v>
       </c>
       <c r="L28" s="22">
-        <f>MAX(I28:K28)</f>
+        <f t="shared" si="0"/>
         <v>0.72</v>
       </c>
       <c r="M28" s="20">
@@ -8968,7 +10192,7 @@
         <v>0.29099999999999998</v>
       </c>
       <c r="P28" s="3">
-        <f>MAX(M28:O28)</f>
+        <f t="shared" si="1"/>
         <v>0.29099999999999998</v>
       </c>
     </row>
@@ -9004,7 +10228,7 @@
         <v>0.66600000000000004</v>
       </c>
       <c r="L29" s="22">
-        <f>MAX(I29:K29)</f>
+        <f t="shared" si="0"/>
         <v>0.67900000000000005</v>
       </c>
       <c r="M29" s="20">
@@ -9017,7 +10241,7 @@
         <v>0.27200000000000002</v>
       </c>
       <c r="P29" s="3">
-        <f>MAX(M29:O29)</f>
+        <f t="shared" si="1"/>
         <v>0.27200000000000002</v>
       </c>
     </row>
@@ -9053,7 +10277,7 @@
         <v>0.63800000000000001</v>
       </c>
       <c r="L30" s="22">
-        <f>MAX(I30:K30)</f>
+        <f t="shared" si="0"/>
         <v>0.69299999999999995</v>
       </c>
       <c r="M30" s="20">
@@ -9066,7 +10290,7 @@
         <v>0.27200000000000002</v>
       </c>
       <c r="P30" s="3">
-        <f>MAX(M30:O30)</f>
+        <f t="shared" si="1"/>
         <v>0.27200000000000002</v>
       </c>
     </row>
@@ -9102,7 +10326,7 @@
         <v>0.63</v>
       </c>
       <c r="L31" s="22">
-        <f>MAX(I31:K31)</f>
+        <f t="shared" si="0"/>
         <v>0.70399999999999996</v>
       </c>
       <c r="M31" s="20">
@@ -9115,7 +10339,7 @@
         <v>0.28799999999999998</v>
       </c>
       <c r="P31" s="3">
-        <f>MAX(M31:O31)</f>
+        <f t="shared" si="1"/>
         <v>0.29099999999999998</v>
       </c>
     </row>
@@ -9151,7 +10375,7 @@
         <v>0.59</v>
       </c>
       <c r="L32" s="22">
-        <f>MAX(I32:K32)</f>
+        <f t="shared" si="0"/>
         <v>0.67</v>
       </c>
       <c r="M32" s="20">
@@ -9164,11 +10388,11 @@
         <v>0.26700000000000002</v>
       </c>
       <c r="P32" s="3">
-        <f>MAX(M32:O32)</f>
+        <f t="shared" si="1"/>
         <v>0.27400000000000002</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>30</v>
       </c>
@@ -9200,7 +10424,7 @@
         <v>0.60599999999999998</v>
       </c>
       <c r="L33" s="22">
-        <f>MAX(I33:K33)</f>
+        <f t="shared" si="0"/>
         <v>0.60599999999999998</v>
       </c>
       <c r="M33" s="20">
@@ -9213,11 +10437,11 @@
         <v>0.215</v>
       </c>
       <c r="P33" s="3">
-        <f>MAX(M33:O33)</f>
+        <f t="shared" si="1"/>
         <v>0.215</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <v>31</v>
       </c>
@@ -9249,7 +10473,7 @@
         <v>0.68400000000000005</v>
       </c>
       <c r="L34" s="22">
-        <f>MAX(I34:K34)</f>
+        <f t="shared" si="0"/>
         <v>0.68400000000000005</v>
       </c>
       <c r="M34" s="20">
@@ -9262,11 +10486,11 @@
         <v>0.27100000000000002</v>
       </c>
       <c r="P34" s="3">
-        <f>MAX(M34:O34)</f>
+        <f t="shared" si="1"/>
         <v>0.27100000000000002</v>
       </c>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>32</v>
       </c>
@@ -9298,7 +10522,7 @@
         <v>0.68500000000000005</v>
       </c>
       <c r="L35" s="22">
-        <f>MAX(I35:K35)</f>
+        <f t="shared" si="0"/>
         <v>0.68500000000000005</v>
       </c>
       <c r="M35" s="20">
@@ -9311,11 +10535,11 @@
         <v>0.26200000000000001</v>
       </c>
       <c r="P35" s="3">
-        <f>MAX(M35:O35)</f>
+        <f t="shared" si="1"/>
         <v>0.26200000000000001</v>
       </c>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <v>33</v>
       </c>
@@ -9344,7 +10568,7 @@
         <v>0.69299999999999995</v>
       </c>
       <c r="L36" s="22">
-        <f>MAX(I36:K36)</f>
+        <f t="shared" si="0"/>
         <v>0.69299999999999995</v>
       </c>
       <c r="M36" s="20">
@@ -9357,11 +10581,11 @@
         <v>0.25</v>
       </c>
       <c r="P36" s="3">
-        <f>MAX(M36:O36)</f>
+        <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <v>34</v>
       </c>
@@ -9390,7 +10614,7 @@
         <v>0.73499999999999999</v>
       </c>
       <c r="L37" s="22">
-        <f>MAX(I37:K37)</f>
+        <f t="shared" si="0"/>
         <v>0.73499999999999999</v>
       </c>
       <c r="M37" s="20">
@@ -9403,11 +10627,11 @@
         <v>0.29499999999999998</v>
       </c>
       <c r="P37" s="3">
-        <f>MAX(M37:O37)</f>
+        <f t="shared" si="1"/>
         <v>0.29499999999999998</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <v>35</v>
       </c>
@@ -9436,7 +10660,7 @@
         <v>0.73299999999999998</v>
       </c>
       <c r="L38" s="22">
-        <f>MAX(I38:K38)</f>
+        <f t="shared" si="0"/>
         <v>0.73299999999999998</v>
       </c>
       <c r="M38" s="20">
@@ -9449,11 +10673,11 @@
         <v>0.28799999999999998</v>
       </c>
       <c r="P38" s="3">
-        <f>MAX(M38:O38)</f>
+        <f t="shared" si="1"/>
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B39" s="1">
         <v>36</v>
       </c>
@@ -9482,7 +10706,7 @@
         <v>0.71399999999999997</v>
       </c>
       <c r="L39" s="22">
-        <f>MAX(I39:K39)</f>
+        <f t="shared" si="0"/>
         <v>0.71399999999999997</v>
       </c>
       <c r="M39" s="20">
@@ -9495,11 +10719,11 @@
         <v>0.3</v>
       </c>
       <c r="P39" s="3">
-        <f>MAX(M39:O39)</f>
+        <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B40" s="1">
         <v>37</v>
       </c>
@@ -9528,7 +10752,7 @@
         <v>0.67100000000000004</v>
       </c>
       <c r="L40" s="22">
-        <f>MAX(I40:K40)</f>
+        <f t="shared" si="0"/>
         <v>0.67100000000000004</v>
       </c>
       <c r="M40" s="20">
@@ -9541,9 +10765,309 @@
         <v>0.252</v>
       </c>
       <c r="P40" s="3">
-        <f>MAX(M40:O40)</f>
+        <f t="shared" si="1"/>
         <v>0.252</v>
       </c>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B41" s="1">
+        <v>38</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41">
+        <v>128</v>
+      </c>
+      <c r="G41">
+        <v>200</v>
+      </c>
+      <c r="H41" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="9">
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="J41" s="18">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="K41" s="18">
+        <v>0.70099999999999996</v>
+      </c>
+      <c r="L41" s="22">
+        <f t="shared" si="0"/>
+        <v>0.70099999999999996</v>
+      </c>
+      <c r="M41" s="9">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="N41" s="2">
+        <v>0.254</v>
+      </c>
+      <c r="O41" s="2">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="P41" s="3">
+        <f t="shared" si="1"/>
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="T41" s="3"/>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B42" s="1">
+        <v>39</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42">
+        <v>256</v>
+      </c>
+      <c r="G42">
+        <v>200</v>
+      </c>
+      <c r="H42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="9">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="J42" s="18">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="K42" s="18">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="L42" s="22">
+        <f t="shared" si="0"/>
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="M42" s="9">
+        <v>0.23</v>
+      </c>
+      <c r="N42" s="2">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="O42" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="P42" s="3">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="T42" s="3"/>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B43" s="1">
+        <v>40</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43">
+        <v>512</v>
+      </c>
+      <c r="G43">
+        <v>200</v>
+      </c>
+      <c r="H43" t="s">
+        <v>13</v>
+      </c>
+      <c r="I43" s="9">
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="J43" s="18">
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="K43" s="18">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="L43" s="22">
+        <f t="shared" si="0"/>
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="M43" s="9">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="N43" s="2">
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="O43" s="2">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="P43" s="3">
+        <f t="shared" si="1"/>
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="T43" s="3"/>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B44" s="1">
+        <v>41</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44">
+        <v>128</v>
+      </c>
+      <c r="G44">
+        <v>200</v>
+      </c>
+      <c r="H44" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="9">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="J44" s="18">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="K44" s="18">
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="L44" s="22">
+        <f t="shared" si="0"/>
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="M44" s="9">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="N44" s="2">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="O44" s="2">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="P44" s="3">
+        <f t="shared" si="1"/>
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="T44" s="3"/>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B45" s="1">
+        <v>42</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45">
+        <v>256</v>
+      </c>
+      <c r="G45">
+        <v>200</v>
+      </c>
+      <c r="H45" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="9">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="J45" s="18">
+        <v>0.71699999999999997</v>
+      </c>
+      <c r="K45" s="18">
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="L45" s="22">
+        <f t="shared" si="0"/>
+        <v>0.71699999999999997</v>
+      </c>
+      <c r="M45" s="9">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="N45" s="2">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="O45" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="P45" s="3">
+        <f t="shared" si="1"/>
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="T45" s="3"/>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B46" s="1">
+        <v>43</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46">
+        <v>512</v>
+      </c>
+      <c r="G46">
+        <v>200</v>
+      </c>
+      <c r="H46" t="s">
+        <v>13</v>
+      </c>
+      <c r="I46" s="9">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="J46" s="18">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="K46" s="18">
+        <v>0.621</v>
+      </c>
+      <c r="L46" s="22">
+        <f t="shared" si="0"/>
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="M46" s="9">
+        <v>0.222</v>
+      </c>
+      <c r="N46" s="2">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="O46" s="2">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="P46" s="3">
+        <f t="shared" si="1"/>
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="T46" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="B3:P40" xr:uid="{CE3605DF-CC1B-4120-B106-3EBE857924BB}">
@@ -9555,8 +11079,8 @@
     <mergeCell ref="I2:L2"/>
     <mergeCell ref="M2:P2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I4:L40">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="J41:L46 I4:L40">
+    <cfRule type="colorScale" priority="153">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9567,8 +11091,44 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:P40">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="N41:P46 M4:P40">
+    <cfRule type="colorScale" priority="158">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T41:T46">
+    <cfRule type="colorScale" priority="163">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:L46">
+    <cfRule type="colorScale" priority="203">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M4:P46">
+    <cfRule type="colorScale" priority="205">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
